--- a/NOD modell.xlsx
+++ b/NOD modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D985A2EB-D4DB-A04C-A2F5-B9BBED8571F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1621CB-205B-B94E-9760-1014E3D588A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="740" windowWidth="29320" windowHeight="17180" activeTab="1" xr2:uid="{6F97247D-DFFC-694E-BCA1-1702AEAD64F0}"/>
+    <workbookView xWindow="25200" yWindow="500" windowWidth="26000" windowHeight="26700" activeTab="3" xr2:uid="{6F97247D-DFFC-694E-BCA1-1702AEAD64F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -46,6 +46,7 @@
     <author>tc={82328C62-DF8F-C24F-8307-F40892C93A4A}</author>
     <author>tc={B895511D-CBA5-9C4E-96D1-6E733BD402FA}</author>
     <author>tc={19E1B78D-9560-4840-9DD5-8156DEB6E121}</author>
+    <author>tc={EEBB5E24-2C64-1440-A49A-7303AE7989A9}</author>
     <author>tc={EE9F1452-F91E-5E46-A17A-C9B6B94B30DB}</author>
   </authors>
   <commentList>
@@ -75,7 +76,16 @@
 </t>
       </text>
     </comment>
-    <comment ref="R75" authorId="3" shapeId="0" xr:uid="{EE9F1452-F91E-5E46-A17A-C9B6B94B30DB}">
+    <comment ref="V4" authorId="3" shapeId="0" xr:uid="{EEBB5E24-2C64-1440-A49A-7303AE7989A9}">
+      <text>
+        <t xml:space="preserve">[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    220-240
+</t>
+      </text>
+    </comment>
+    <comment ref="R75" authorId="4" shapeId="0" xr:uid="{EE9F1452-F91E-5E46-A17A-C9B6B94B30DB}">
       <text>
         <t>[Kommentartråd]
 Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
@@ -146,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="285">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -825,29 +835,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>Bluetooth og Zigbee</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Long-range</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Trådløs kommunikasjon over lange distanser, hovedsaklig via mobielneett (Cellular IoT) (Satser på lønnsomhet ila 28)</t>
     </r>
   </si>
   <si>
@@ -1367,6 +1354,38 @@
   </si>
   <si>
     <t>Accured and other liabilities</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Long-range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Trådløs kommunikasjon over lange distanser, hovedsaklig via mobilnett (Cellular IoT) (Satser på lønnsomhet ila 28)</t>
+    </r>
+  </si>
+  <si>
+    <t>07.08.26: Kvalitetsdirektør kjøper 1 100 aksjer og styremedlem har kjøpt 1 200 aksjer</t>
+  </si>
+  <si>
+    <t>19.08.26: CEO Wollan kjøper 5000 aksjer til 160,87kr</t>
+  </si>
+  <si>
+    <t>25.08.26: EVP Short range Øyvind Strøm kjøper 2000 aksjer 160,80kr</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1683,7 +1702,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1692,7 +1710,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2312,6 +2329,10 @@
     <text xml:space="preserve">200-220 m
 </text>
   </threadedComment>
+  <threadedComment ref="V4" dT="2026-08-07T06:45:58.74" personId="{03F14725-5B14-A646-93A0-04AC69440968}" id="{EEBB5E24-2C64-1440-A49A-7303AE7989A9}">
+    <text xml:space="preserve">220-240
+</text>
+  </threadedComment>
   <threadedComment ref="R75" dT="2025-10-29T07:36:15.69" personId="{5FDE49D1-A79D-D045-9A2E-7E4A896E15B4}" id="{EE9F1452-F91E-5E46-A17A-C9B6B94B30DB}">
     <text>Oppkjøp på -106,547</text>
   </threadedComment>
@@ -2371,520 +2392,535 @@
   <dimension ref="A2:Z86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" style="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="10.83203125" style="42"/>
-    <col min="7" max="7" width="13.1640625" style="42" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.83203125" style="42"/>
-    <col min="10" max="10" width="12.5" style="42" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" style="42" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="53.33203125" style="42" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.83203125" style="42" customWidth="1"/>
-    <col min="14" max="14" width="13.5" style="42" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="42"/>
+    <col min="1" max="1" width="16.33203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="10.83203125" style="40"/>
+    <col min="7" max="7" width="13.1640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.83203125" style="40"/>
+    <col min="10" max="10" width="12.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53.33203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.83203125" style="40" customWidth="1"/>
+    <col min="14" max="14" width="13.5" style="40" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="40"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="43" t="s">
+      <c r="P2" s="41" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="P3" s="40" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="P4" s="40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="P5" s="40" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="42"/>
+      <c r="P6" s="40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="42"/>
+      <c r="P7" s="40" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" s="44"/>
-      <c r="P4" s="42" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="42"/>
+      <c r="P8" s="40" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="P5" s="42" t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="41"/>
+      <c r="B9" s="43"/>
+      <c r="P9" s="40" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="44"/>
-      <c r="P6" s="42" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P10" s="40" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P11" s="40" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P12" s="40" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P13" s="40" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J14" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="K14" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="L14" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="M14" s="50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J15" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="K15" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="L15" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="M15" s="51" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J16" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="K16" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="L16" s="54" t="s">
+        <v>208</v>
+      </c>
+      <c r="M16" s="54" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J17" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="K17" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="L17" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="M17" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="N17" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="O17" s="40" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J18" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="K18" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="L18" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="M18" s="57" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J19" s="61" t="s">
+        <v>213</v>
+      </c>
+      <c r="K19" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="L19" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="M19" s="60" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J20" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="K20" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="L20" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="M20" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="N20" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="O20" s="40" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J21" s="64" t="s">
+        <v>221</v>
+      </c>
+      <c r="K21" s="65" t="s">
+        <v>222</v>
+      </c>
+      <c r="L21" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="M21" s="63" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="J22" s="67" t="s">
+        <v>221</v>
+      </c>
+      <c r="K22" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L22" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="M22" s="66" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="K32" s="40" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A34" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="40" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A35" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="P7" s="42" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="P8" s="42" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
-      <c r="B9" s="45"/>
-      <c r="P9" s="42" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="P10" s="42" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J14" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="K14" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="L14" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="M14" s="52" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J15" s="54" t="s">
-        <v>204</v>
-      </c>
-      <c r="K15" s="55" t="s">
-        <v>205</v>
-      </c>
-      <c r="L15" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="M15" s="53" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J16" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="K16" s="58" t="s">
-        <v>208</v>
-      </c>
-      <c r="L16" s="56" t="s">
-        <v>209</v>
-      </c>
-      <c r="M16" s="56" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J17" s="54" t="s">
-        <v>204</v>
-      </c>
-      <c r="K17" s="55" t="s">
-        <v>211</v>
-      </c>
-      <c r="L17" s="53" t="s">
-        <v>212</v>
-      </c>
-      <c r="M17" s="53" t="s">
-        <v>213</v>
-      </c>
-      <c r="N17" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="O17" s="42" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J18" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="K18" s="61" t="s">
-        <v>215</v>
-      </c>
-      <c r="L18" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="M18" s="59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J19" s="63" t="s">
-        <v>214</v>
-      </c>
-      <c r="K19" s="64" t="s">
-        <v>218</v>
-      </c>
-      <c r="L19" s="62" t="s">
-        <v>219</v>
-      </c>
-      <c r="M19" s="62" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J20" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="K20" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="L20" s="59" t="s">
-        <v>221</v>
-      </c>
-      <c r="M20" s="59" t="s">
-        <v>246</v>
-      </c>
-      <c r="N20" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="O20" s="42" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J21" s="66" t="s">
-        <v>222</v>
-      </c>
-      <c r="K21" s="67" t="s">
-        <v>223</v>
-      </c>
-      <c r="L21" s="65" t="s">
-        <v>224</v>
-      </c>
-      <c r="M21" s="65" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="J22" s="69" t="s">
-        <v>222</v>
-      </c>
-      <c r="K22" s="70" t="s">
-        <v>226</v>
-      </c>
-      <c r="L22" s="68" t="s">
+      <c r="Z35" s="40" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A36" s="40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A37" s="40" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A38" s="40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A40" s="41" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A41" s="40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A42" s="40" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A43" s="40" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A44" s="40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A46" s="41" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A47" s="40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A48" s="40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="40" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="41" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="49" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="49" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="49" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="49" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="49" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="41" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="40" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="40" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="40" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="41" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="40" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="40" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="49" t="s">
         <v>227</v>
       </c>
-      <c r="M22" s="68" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="42" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="42" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="42" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="42" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="42" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="K32" s="42" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A34" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="B34" s="42" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A35" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="Z35" s="42" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A36" s="42" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A37" s="42" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A38" s="42" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A40" s="43" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A41" s="42" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A42" s="42" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A43" s="42" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A44" s="42" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A46" s="43" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A47" s="42" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A48" s="42" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="42" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="42" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="43" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="51" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="51" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="51" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="51" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="43" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="51" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="51" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="51" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="51" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="43" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="42" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="42" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="42" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="42" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="43" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="42" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="42" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="42" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="42" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="51" t="s">
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="49" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="51" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="49" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="51" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="49" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="51" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="49" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="51" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="49" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="51" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="49" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="51" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="49" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="51" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="49" t="s">
         <v>235</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="51" t="s">
-        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -2920,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>3</v>
@@ -2971,16 +3007,16 @@
         <v>93</v>
       </c>
       <c r="T3" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="U3" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="U3" s="21" t="s">
+      <c r="V3" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="W3" s="21" t="s">
         <v>182</v>
-      </c>
-      <c r="W3" s="21" t="s">
-        <v>183</v>
       </c>
       <c r="X3" s="21"/>
       <c r="Y3" s="21" t="s">
@@ -3040,7 +3076,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="8">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
@@ -3097,7 +3133,7 @@
         <v>192.44300000000001</v>
       </c>
       <c r="U4" s="16">
-        <v>210</v>
+        <v>218.566</v>
       </c>
       <c r="V4" s="16"/>
       <c r="W4" s="16"/>
@@ -3171,7 +3207,7 @@
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="76">
+      <c r="B5" s="74">
         <v>199.8</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3228,7 +3264,9 @@
       <c r="T5" s="18">
         <v>-92.155000000000001</v>
       </c>
-      <c r="U5" s="18"/>
+      <c r="U5" s="18">
+        <v>-102.48399999999999</v>
+      </c>
       <c r="V5" s="18"/>
       <c r="W5" s="16"/>
       <c r="X5" s="18"/>
@@ -3303,7 +3341,7 @@
       </c>
       <c r="B6" s="8">
         <f>B4*B5</f>
-        <v>30169.800000000003</v>
+        <v>35364.6</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>21</v>
@@ -3373,10 +3411,13 @@
         <v>93.508999999999986</v>
       </c>
       <c r="T6" s="18">
-        <f t="shared" ref="T6" si="4">SUM(T4:T5)</f>
+        <f t="shared" ref="T6:U6" si="4">SUM(T4:T5)</f>
         <v>100.28800000000001</v>
       </c>
-      <c r="U6" s="18"/>
+      <c r="U6" s="18">
+        <f t="shared" si="4"/>
+        <v>116.08200000000001</v>
+      </c>
       <c r="V6" s="18"/>
       <c r="W6" s="16"/>
       <c r="X6" s="18"/>
@@ -3510,7 +3551,9 @@
       <c r="T7" s="18">
         <v>-56.156999999999996</v>
       </c>
-      <c r="U7" s="18"/>
+      <c r="U7" s="18">
+        <v>-56.905000000000001</v>
+      </c>
       <c r="V7" s="18"/>
       <c r="W7" s="16"/>
       <c r="X7" s="18"/>
@@ -3640,7 +3683,9 @@
       <c r="T8" s="18">
         <v>-22.867999999999999</v>
       </c>
-      <c r="U8" s="18"/>
+      <c r="U8" s="18">
+        <v>-25.510999999999999</v>
+      </c>
       <c r="V8" s="18"/>
       <c r="W8" s="16"/>
       <c r="X8" s="18"/>
@@ -3713,9 +3758,9 @@
       <c r="A9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="50">
+      <c r="B9" s="48">
         <f>B6-B7+B8</f>
-        <v>25384.224000000006</v>
+        <v>30579.024000000001</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>24</v>
@@ -3785,10 +3830,13 @@
         <v>15.445999999999984</v>
       </c>
       <c r="T9" s="16">
-        <f t="shared" ref="T9" si="11">SUM(T6:T8)</f>
+        <f t="shared" ref="T9:U9" si="11">SUM(T6:T8)</f>
         <v>21.263000000000016</v>
       </c>
-      <c r="U9" s="18"/>
+      <c r="U9" s="16">
+        <f t="shared" si="11"/>
+        <v>33.666000000000011</v>
+      </c>
       <c r="V9" s="18"/>
       <c r="W9" s="16"/>
       <c r="X9" s="18"/>
@@ -3916,7 +3964,9 @@
       <c r="T10" s="18">
         <v>-11.17</v>
       </c>
-      <c r="U10" s="18"/>
+      <c r="U10" s="18">
+        <v>-11.36</v>
+      </c>
       <c r="V10" s="18"/>
       <c r="W10" s="16"/>
       <c r="X10" s="18"/>
@@ -4050,10 +4100,13 @@
         <v>2.004999999999983</v>
       </c>
       <c r="T11" s="16">
-        <f t="shared" ref="T11" si="16">SUM(T9:T10)</f>
+        <f t="shared" ref="T11:U11" si="16">SUM(T9:T10)</f>
         <v>10.093000000000016</v>
       </c>
-      <c r="U11" s="18"/>
+      <c r="U11" s="16">
+        <f t="shared" si="16"/>
+        <v>22.306000000000012</v>
+      </c>
       <c r="V11" s="18"/>
       <c r="W11" s="16"/>
       <c r="X11" s="18"/>
@@ -4181,7 +4234,9 @@
       <c r="T12" s="18">
         <v>0</v>
       </c>
-      <c r="U12" s="18"/>
+      <c r="U12" s="18">
+        <v>0</v>
+      </c>
       <c r="V12" s="18"/>
       <c r="W12" s="16"/>
       <c r="X12" s="18"/>
@@ -4240,9 +4295,9 @@
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B13" s="71">
+        <v>236</v>
+      </c>
+      <c r="B13" s="69">
         <f>(T51-T42)/AF9</f>
         <v>-1.6832324569699262</v>
       </c>
@@ -4300,7 +4355,9 @@
       <c r="T13" s="18">
         <v>-1.1950000000000001</v>
       </c>
-      <c r="U13" s="18"/>
+      <c r="U13" s="18">
+        <v>-0.63600000000000001</v>
+      </c>
       <c r="V13" s="18"/>
       <c r="W13" s="16"/>
       <c r="X13" s="18"/>
@@ -4417,7 +4474,9 @@
       <c r="T14" s="18">
         <v>0.67900000000000005</v>
       </c>
-      <c r="U14" s="18"/>
+      <c r="U14" s="18">
+        <v>0</v>
+      </c>
       <c r="V14" s="18"/>
       <c r="W14" s="16"/>
       <c r="X14" s="18"/>
@@ -4545,10 +4604,13 @@
         <v>0.19799999999998308</v>
       </c>
       <c r="T15" s="18">
-        <f t="shared" ref="T15" si="21">SUM(T11:T14)</f>
+        <f t="shared" ref="T15:U15" si="21">SUM(T11:T14)</f>
         <v>9.5770000000000159</v>
       </c>
-      <c r="U15" s="18"/>
+      <c r="U15" s="18">
+        <f t="shared" si="21"/>
+        <v>21.670000000000012</v>
+      </c>
       <c r="V15" s="18"/>
       <c r="W15" s="16"/>
       <c r="X15" s="18"/>
@@ -4676,7 +4738,9 @@
       <c r="T16" s="18">
         <v>1</v>
       </c>
-      <c r="U16" s="18"/>
+      <c r="U16" s="18">
+        <v>-5.2169999999999996</v>
+      </c>
       <c r="V16" s="18"/>
       <c r="W16" s="16"/>
       <c r="X16" s="18"/>
@@ -4814,10 +4878,13 @@
         <v>4.6469999999999825</v>
       </c>
       <c r="T17" s="16">
-        <f t="shared" ref="T17" si="27">SUM(T15:T16)</f>
+        <f t="shared" ref="T17:U17" si="27">SUM(T15:T16)</f>
         <v>10.577000000000016</v>
       </c>
-      <c r="U17" s="18"/>
+      <c r="U17" s="16">
+        <f t="shared" si="27"/>
+        <v>16.453000000000014</v>
+      </c>
       <c r="V17" s="18"/>
       <c r="W17" s="16"/>
       <c r="X17" s="18"/>
@@ -5879,36 +5946,40 @@
         <v>-0.19778930442450449</v>
       </c>
       <c r="P18" s="10">
-        <f>(P17*$B$11)/P19</f>
+        <f t="shared" ref="P18:U18" si="35">(P17*$B$11)/P19</f>
         <v>5.9474039109913286E-2</v>
       </c>
       <c r="Q18" s="10">
-        <f>(Q17*$B$11)/Q19</f>
+        <f t="shared" si="35"/>
         <v>0.51666165257534113</v>
       </c>
       <c r="R18" s="10">
-        <f>(R17*$B$11)/R19</f>
+        <f t="shared" si="35"/>
         <v>4.655183460338707E-2</v>
       </c>
       <c r="S18" s="10">
-        <f>(S17*$B$11)/S19</f>
+        <f t="shared" si="35"/>
         <v>0.22795192350046167</v>
       </c>
       <c r="T18" s="10">
-        <f>(T17*$B$11)/T19</f>
+        <f t="shared" si="35"/>
         <v>0.51883957281351312</v>
+      </c>
+      <c r="U18" s="10">
+        <f t="shared" si="35"/>
+        <v>0.80707832953585379</v>
       </c>
       <c r="W18" s="16"/>
       <c r="Y18" s="10">
-        <f t="shared" ref="Y18:AA18" si="35">(Y17*$B$11)/Y19</f>
+        <f t="shared" ref="Y18:AA18" si="36">(Y17*$B$11)/Y19</f>
         <v>0.43051464335521539</v>
       </c>
       <c r="Z18" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.9674089900567011</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.6420654572580058</v>
       </c>
       <c r="AB18" s="10">
@@ -5932,39 +6003,39 @@
         <v>2.5153295398575248</v>
       </c>
       <c r="AG18" s="10">
-        <f t="shared" ref="AG18:AO18" si="36">(AG17*$B$11)/AG19</f>
+        <f t="shared" ref="AG18:AO18" si="37">(AG17*$B$11)/AG19</f>
         <v>4.2542969162325273</v>
       </c>
       <c r="AH18" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>6.4257606292471401</v>
       </c>
       <c r="AI18" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9.12656908940804</v>
       </c>
       <c r="AJ18" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>12.47443608649985</v>
       </c>
       <c r="AK18" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>16.612345168702401</v>
       </c>
       <c r="AL18" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>21.713871505638991</v>
       </c>
       <c r="AM18" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>27.98961056941824</v>
       </c>
       <c r="AN18" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>35.694941767508155</v>
       </c>
       <c r="AO18" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45.139401870235567</v>
       </c>
     </row>
@@ -6021,6 +6092,9 @@
         <v>199.7816</v>
       </c>
       <c r="T19" s="7">
+        <v>199.7816</v>
+      </c>
+      <c r="U19" s="7">
         <v>199.7816</v>
       </c>
       <c r="W19" s="16"/>
@@ -6107,71 +6181,71 @@
         <v>0.12</v>
       </c>
       <c r="H21" s="12">
-        <f t="shared" ref="H21:K21" si="37">(H4-D4)/D4</f>
+        <f t="shared" ref="H21:K21" si="38">(H4-D4)/D4</f>
         <v>-0.20568476016735313</v>
       </c>
       <c r="I21" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-0.22963529100291225</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-0.33181748454873389</v>
       </c>
       <c r="K21" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-0.43465152006019625</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ref="L21:P21" si="38">(L4-H4)/H4</f>
+        <f t="shared" ref="L21:P21" si="39">(L4-H4)/H4</f>
         <v>-0.48773276122892423</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-0.17033141612143934</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.17582629174041509</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.38825986893791642</v>
       </c>
       <c r="P21" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1.0815055437729872</v>
       </c>
       <c r="Q21" s="12">
-        <f t="shared" ref="Q21" si="39">(Q4-M4)/M4</f>
+        <f t="shared" ref="Q21" si="40">(Q4-M4)/M4</f>
         <v>0.28176070152951571</v>
       </c>
       <c r="R21" s="12">
-        <f t="shared" ref="R21" si="40">(R4-N4)/N4</f>
+        <f t="shared" ref="R21" si="41">(R4-N4)/N4</f>
         <v>0.12739571589627963</v>
       </c>
       <c r="S21" s="12">
-        <f t="shared" ref="S21:U21" si="41">(S4-O4)/O4</f>
+        <f t="shared" ref="S21:U21" si="42">(S4-O4)/O4</f>
         <v>0.12855525965379494</v>
       </c>
       <c r="T21" s="12">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.24102329300693887</v>
       </c>
       <c r="U21" s="12">
-        <f t="shared" si="41"/>
-        <v>0.28048780487804881</v>
+        <f t="shared" si="42"/>
+        <v>0.33271951219512197</v>
       </c>
       <c r="Z21" s="12">
-        <f t="shared" ref="Z21:AB21" si="42">(Z4-Y4)/Y4</f>
+        <f t="shared" ref="Z21:AB21" si="43">(Z4-Y4)/Y4</f>
         <v>0.40507637094956572</v>
       </c>
       <c r="AA21" s="12">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.50666926609693086</v>
       </c>
       <c r="AB21" s="12">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.27223321452906341</v>
       </c>
       <c r="AC21" s="12">
@@ -6187,43 +6261,43 @@
         <v>0.30616714246607479</v>
       </c>
       <c r="AF21" s="13">
-        <f t="shared" ref="AF21:AO21" si="43">(AF4-AE4)/AE4</f>
+        <f t="shared" ref="AF21:AO21" si="44">(AF4-AE4)/AE4</f>
         <v>0.25</v>
       </c>
       <c r="AG21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.2</v>
       </c>
       <c r="AH21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.19999999999999987</v>
       </c>
       <c r="AI21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="AJ21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="AK21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AL21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.1999999999999999</v>
       </c>
       <c r="AM21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.19999999999999993</v>
       </c>
       <c r="AN21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="AO21" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
@@ -6233,72 +6307,72 @@
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="11">
-        <f t="shared" ref="E22:P22" si="44">(E4-D4)/D4</f>
+        <f t="shared" ref="E22:P22" si="45">(E4-D4)/D4</f>
         <v>9.3404192565242558E-2</v>
       </c>
       <c r="F22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>9.4911257973793357E-3</v>
       </c>
       <c r="G22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-5.3011821641174316E-2</v>
       </c>
       <c r="H22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-0.24008486001233187</v>
       </c>
       <c r="I22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>6.0435404461314297E-2</v>
       </c>
       <c r="J22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-0.12440911183591954</v>
       </c>
       <c r="K22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-0.19875436010990075</v>
       </c>
       <c r="L22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-0.31143419629735747</v>
       </c>
       <c r="M22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.71748234851942316</v>
       </c>
       <c r="N22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.2409084869752792</v>
       </c>
       <c r="O22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-5.3995326661334157E-2</v>
       </c>
       <c r="P22" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>3.2410119840213206E-2</v>
       </c>
       <c r="Q22" s="11">
-        <f t="shared" ref="Q22" si="45">(Q4-P4)/P4</f>
+        <f t="shared" ref="Q22" si="46">(Q4-P4)/P4</f>
         <v>5.76005365388087E-2</v>
       </c>
       <c r="R22" s="11">
-        <f t="shared" ref="R22" si="46">(R4-Q4)/Q4</f>
+        <f t="shared" ref="R22" si="47">(R4-Q4)/Q4</f>
         <v>9.1463414634146339E-2</v>
       </c>
       <c r="S22" s="11">
-        <f t="shared" ref="S22:U22" si="47">(S4-R4)/R4</f>
+        <f t="shared" ref="S22:U22" si="48">(S4-R4)/R4</f>
         <v>-5.3022346368715161E-2</v>
       </c>
       <c r="T22" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.13529665091529081</v>
       </c>
       <c r="U22" s="11">
-        <f t="shared" si="47"/>
-        <v>9.1232209017735058E-2</v>
+        <f t="shared" si="48"/>
+        <v>0.13574409045795371</v>
       </c>
       <c r="AC22" s="12"/>
       <c r="AD22" s="12"/>
@@ -6312,90 +6386,90 @@
     </row>
     <row r="23" spans="3:275" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D23" s="14">
-        <f t="shared" ref="D23:P23" si="48">D6/D4</f>
+        <f t="shared" ref="D23:P23" si="49">D6/D4</f>
         <v>0.59711283222092348</v>
       </c>
       <c r="E23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.55368230704291488</v>
       </c>
       <c r="F23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.57270878384062307</v>
       </c>
       <c r="G23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.52720850272241782</v>
       </c>
       <c r="H23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.53328107379596779</v>
       </c>
       <c r="I23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.53005829448115327</v>
       </c>
       <c r="J23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.50474335522953995</v>
       </c>
       <c r="K23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.51996894438642061</v>
       </c>
       <c r="L23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.47987865446052247</v>
       </c>
       <c r="M23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.42025338220697311</v>
       </c>
       <c r="N23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.4954116883853048</v>
       </c>
       <c r="O23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.49130492676431414</v>
       </c>
       <c r="P23" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.49548585136843198</v>
       </c>
       <c r="Q23" s="14">
-        <f t="shared" ref="Q23:S23" si="49">Q6/Q4</f>
+        <f t="shared" ref="Q23:S23" si="50">Q6/Q4</f>
         <v>0.50738414634146345</v>
       </c>
       <c r="R23" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.51955307262569828</v>
       </c>
       <c r="S23" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.55164622527417417</v>
       </c>
       <c r="T23" s="14">
-        <f t="shared" ref="T23:U23" si="50">T6/T4</f>
+        <f t="shared" ref="T23:U23" si="51">T6/T4</f>
         <v>0.52113093227605056</v>
       </c>
       <c r="U23" s="14">
-        <f t="shared" si="50"/>
-        <v>0</v>
+        <f t="shared" si="51"/>
+        <v>0.53110730854753263</v>
       </c>
       <c r="Y23" s="14">
-        <f t="shared" ref="Y23:AA23" si="51">Y6/Y4</f>
+        <f t="shared" ref="Y23:AA23" si="52">Y6/Y4</f>
         <v>0.51008165883597145</v>
       </c>
       <c r="Z23" s="14">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.52941263569889707</v>
       </c>
       <c r="AA23" s="14">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.53578705644949942</v>
       </c>
       <c r="AB23" s="14">
@@ -6415,43 +6489,43 @@
         <v>0.51946107784431139</v>
       </c>
       <c r="AF23" s="15">
-        <f t="shared" ref="AF23:AO23" si="52">AF6/AF4</f>
+        <f t="shared" ref="AF23:AO23" si="53">AF6/AF4</f>
         <v>0.52</v>
       </c>
       <c r="AG23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AH23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AI23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AJ23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AK23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AL23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AM23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AN23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AO23" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.52</v>
       </c>
       <c r="AQ23" s="1" t="s">
@@ -6470,47 +6544,47 @@
         <v>0.29894694296669327</v>
       </c>
       <c r="E24" s="14">
-        <f t="shared" ref="E24:O24" si="53">E9/E4</f>
+        <f t="shared" ref="E24:O24" si="54">E9/E4</f>
         <v>0.2594024587011145</v>
       </c>
       <c r="F24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.29756985852627826</v>
       </c>
       <c r="G24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.20312581646409644</v>
       </c>
       <c r="H24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.1000907665648981</v>
       </c>
       <c r="I24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.18491476296387568</v>
       </c>
       <c r="J24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>9.5133710036954505E-2</v>
       </c>
       <c r="K24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-6.3664007837845343E-2</v>
       </c>
       <c r="L24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-0.30646460307659257</v>
       </c>
       <c r="M24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-5.6522520691838149E-2</v>
       </c>
       <c r="N24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.10181202093554952</v>
       </c>
       <c r="O24" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>5.7716378162449934E-2</v>
       </c>
       <c r="P24" s="14">
@@ -6518,91 +6592,91 @@
         <v>9.506797018082401E-2</v>
       </c>
       <c r="Q24" s="14">
-        <f t="shared" ref="Q24:S24" si="54">Q9/Q4</f>
+        <f t="shared" ref="Q24:S24" si="55">Q9/Q4</f>
         <v>0.12695121951219512</v>
       </c>
       <c r="R24" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>8.7368715083798898E-2</v>
       </c>
       <c r="S24" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>9.1122005321251295E-2</v>
       </c>
       <c r="T24" s="14">
-        <f t="shared" ref="T24:U24" si="55">T9/T4</f>
+        <f t="shared" ref="T24:U24" si="56">T9/T4</f>
         <v>0.11048985933497199</v>
       </c>
       <c r="U24" s="14">
-        <f t="shared" si="55"/>
-        <v>0</v>
+        <f t="shared" si="56"/>
+        <v>0.15403127659379781</v>
       </c>
       <c r="Y24" s="14">
         <f>Y9/Y4</f>
         <v>0.1149777215277657</v>
       </c>
       <c r="Z24" s="14">
-        <f t="shared" ref="Z24:AO24" si="56">Z9/Z4</f>
+        <f t="shared" ref="Z24:AO24" si="57">Z9/Z4</f>
         <v>0.19091499122692285</v>
       </c>
       <c r="AA24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.20521417527124061</v>
       </c>
       <c r="AB24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.26478820291116395</v>
       </c>
       <c r="AC24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>9.0318290416288388E-2</v>
       </c>
       <c r="AD24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>-1.0224473035860934E-2</v>
       </c>
       <c r="AE24" s="14">
-        <f t="shared" ref="AE24" si="57">AE9/AE4</f>
+        <f t="shared" ref="AE24" si="58">AE9/AE4</f>
         <v>0.10029940119760479</v>
       </c>
       <c r="AF24" s="15">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.12663473053892216</v>
       </c>
       <c r="AG24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.15088742514970063</v>
       </c>
       <c r="AH24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.17293913173652697</v>
       </c>
       <c r="AI24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.1930372871756488</v>
       </c>
       <c r="AJ24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.21139932162134076</v>
       </c>
       <c r="AK24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.2282163785832329</v>
       </c>
       <c r="AL24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.2436565710194033</v>
       </c>
       <c r="AM24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.2578678314090832</v>
       </c>
       <c r="AN24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.27098040652448296</v>
       </c>
       <c r="AO24" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.28310904128240649</v>
       </c>
       <c r="AQ24" s="1" t="s">
@@ -6615,146 +6689,146 @@
     </row>
     <row r="25" spans="3:275" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D25" s="14">
-        <f t="shared" ref="D25:T25" si="58">D11/D4</f>
+        <f t="shared" ref="D25:T25" si="59">D11/D4</f>
         <v>0.24412024950023489</v>
       </c>
       <c r="E25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.20670173387882337</v>
       </c>
       <c r="F25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.24003523235042329</v>
       </c>
       <c r="G25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.14119472864652455</v>
       </c>
       <c r="H25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>2.0951948730643346E-2</v>
       </c>
       <c r="I25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.11400818327421759</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.5544578652309496E-2</v>
       </c>
       <c r="K25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>-0.16660042701468675</v>
       </c>
       <c r="L25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>-0.44948857687454691</v>
       </c>
       <c r="M25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>-0.13125542208223587</v>
       </c>
       <c r="N25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3.8954986049265318E-2</v>
       </c>
       <c r="O25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>-1.1371504660452874E-2</v>
       </c>
       <c r="P25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3.6835452833595704E-2</v>
       </c>
       <c r="Q25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6.9871951219512188E-2</v>
       </c>
       <c r="R25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>2.4798882681564265E-2</v>
       </c>
       <c r="S25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.182828050427991E-2</v>
       </c>
       <c r="T25" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>5.2446698502933417E-2</v>
       </c>
       <c r="U25" s="14">
         <f>U11/U4</f>
-        <v>0</v>
+        <v>0.10205612949864119</v>
       </c>
       <c r="Y25" s="14">
-        <f t="shared" ref="Y25:AO25" si="59">Y11/Y4</f>
+        <f t="shared" ref="Y25:AO25" si="60">Y11/Y4</f>
         <v>3.3370897553702338E-2</v>
       </c>
       <c r="Z25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.11441277142864192</v>
       </c>
       <c r="AA25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.14330382881702391</v>
       </c>
       <c r="AB25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.20805449484636954</v>
       </c>
       <c r="AC25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>8.6632318294101521E-3</v>
       </c>
       <c r="AD25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-8.9560439560439548E-2</v>
       </c>
       <c r="AE25" s="14">
-        <f t="shared" ref="AE25" si="60">AE11/AE4</f>
+        <f t="shared" ref="AE25" si="61">AE11/AE4</f>
         <v>3.5928143712574849E-2</v>
       </c>
       <c r="AF25" s="15">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>7.8730538922155702E-2</v>
       </c>
       <c r="AG25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.11096726546906191</v>
       </c>
       <c r="AH25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.13967233200266135</v>
       </c>
       <c r="AI25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.16531495406409413</v>
       </c>
       <c r="AJ25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.18829737736171187</v>
       </c>
       <c r="AK25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.20896475836687547</v>
       </c>
       <c r="AL25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.22761355417243878</v>
       </c>
       <c r="AM25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.24449865070327942</v>
       </c>
       <c r="AN25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25983942260297982</v>
       </c>
       <c r="AO25" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.27382488801448723</v>
       </c>
       <c r="AQ25" s="26" t="s">
@@ -6850,7 +6924,7 @@
       </c>
       <c r="AR28" s="12">
         <f>(AR27-B4)/B4</f>
-        <v>1.0491448563274941</v>
+        <v>0.74814052714944412</v>
       </c>
     </row>
     <row r="29" spans="3:275" x14ac:dyDescent="0.25">
@@ -6922,7 +6996,9 @@
       <c r="T30" s="18">
         <v>101.29600000000001</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="18">
+        <v>101.294</v>
+      </c>
       <c r="V30" s="18"/>
       <c r="W30" s="18"/>
       <c r="X30" s="18"/>
@@ -7014,7 +7090,9 @@
       <c r="T31" s="18">
         <v>53.219000000000001</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="18">
+        <v>52.892000000000003</v>
+      </c>
       <c r="V31" s="18"/>
       <c r="W31" s="18"/>
       <c r="X31" s="18"/>
@@ -7107,7 +7185,9 @@
       <c r="T32" s="18">
         <v>52.5</v>
       </c>
-      <c r="U32" s="18"/>
+      <c r="U32" s="18">
+        <v>51.792999999999999</v>
+      </c>
       <c r="V32" s="18"/>
       <c r="W32" s="18"/>
       <c r="X32" s="18"/>
@@ -7200,7 +7280,9 @@
       <c r="T33" s="18">
         <v>27.475000000000001</v>
       </c>
-      <c r="U33" s="18"/>
+      <c r="U33" s="18">
+        <v>22.946999999999999</v>
+      </c>
       <c r="V33" s="18"/>
       <c r="W33" s="18"/>
       <c r="X33" s="18"/>
@@ -7293,7 +7375,9 @@
       <c r="T34" s="18">
         <v>34.078000000000003</v>
       </c>
-      <c r="U34" s="18"/>
+      <c r="U34" s="18">
+        <v>36.956000000000003</v>
+      </c>
       <c r="V34" s="18"/>
       <c r="W34" s="18"/>
       <c r="X34" s="18"/>
@@ -7386,7 +7470,9 @@
       <c r="T35" s="18">
         <v>49.506999999999998</v>
       </c>
-      <c r="U35" s="18"/>
+      <c r="U35" s="18">
+        <v>47.402999999999999</v>
+      </c>
       <c r="V35" s="18"/>
       <c r="W35" s="18"/>
       <c r="X35" s="18"/>
@@ -7479,7 +7565,9 @@
       <c r="T36" s="18">
         <v>0</v>
       </c>
-      <c r="U36" s="18"/>
+      <c r="U36" s="18">
+        <v>0</v>
+      </c>
       <c r="V36" s="18"/>
       <c r="W36" s="18"/>
       <c r="X36" s="18"/>
@@ -7572,7 +7660,9 @@
       <c r="T37" s="18">
         <v>90.417000000000002</v>
       </c>
-      <c r="U37" s="18"/>
+      <c r="U37" s="18">
+        <v>86.984999999999999</v>
+      </c>
       <c r="V37" s="18"/>
       <c r="W37" s="18"/>
       <c r="X37" s="18"/>
@@ -7615,27 +7705,27 @@
         <v>45</v>
       </c>
       <c r="D38" s="23">
-        <f t="shared" ref="D38:M38" si="61">SUM(D30:D37)</f>
+        <f t="shared" ref="D38:M38" si="62">SUM(D30:D37)</f>
         <v>101.95000000000002</v>
       </c>
       <c r="E38" s="23">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>100.55</v>
       </c>
       <c r="F38" s="23">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>101.94999999999999</v>
       </c>
       <c r="G38" s="23">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>101.95000000000002</v>
       </c>
       <c r="H38" s="23">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>209.3</v>
       </c>
       <c r="I38" s="23">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>252.70000000000002</v>
       </c>
       <c r="J38" s="23">
@@ -7643,67 +7733,70 @@
         <v>224.5</v>
       </c>
       <c r="K38" s="23">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>252.70000000000002</v>
       </c>
       <c r="L38" s="23">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>253</v>
       </c>
       <c r="M38" s="23">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>259.12099999999998</v>
       </c>
       <c r="N38" s="23">
-        <f t="shared" ref="N38:T38" si="62">SUM(N30:N37)</f>
+        <f t="shared" ref="N38:U38" si="63">SUM(N30:N37)</f>
         <v>259</v>
       </c>
       <c r="O38" s="23">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>253.44499999999999</v>
       </c>
       <c r="P38" s="23">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>252.625</v>
       </c>
       <c r="Q38" s="23">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>262.911</v>
       </c>
       <c r="R38" s="23">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>399.90099999999995</v>
       </c>
       <c r="S38" s="23">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>400.07600000000002</v>
       </c>
       <c r="T38" s="23">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>408.49199999999996</v>
       </c>
-      <c r="U38" s="18"/>
+      <c r="U38" s="23">
+        <f t="shared" si="63"/>
+        <v>400.27000000000004</v>
+      </c>
       <c r="V38" s="18"/>
       <c r="W38" s="18"/>
       <c r="X38" s="18"/>
       <c r="Y38" s="23">
-        <f t="shared" ref="Y38:AA38" si="63">SUM(Y30:Y37)</f>
+        <f t="shared" ref="Y38:AA38" si="64">SUM(Y30:Y37)</f>
         <v>98.77000000000001</v>
       </c>
       <c r="Z38" s="23">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>104.29300000000002</v>
       </c>
       <c r="AA38" s="23">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>103.21</v>
       </c>
       <c r="AB38" s="23">
-        <f t="shared" ref="AB38" si="64">SUM(AB30:AB37)</f>
+        <f t="shared" ref="AB38" si="65">SUM(AB30:AB37)</f>
         <v>101.95000000000002</v>
       </c>
       <c r="AC38" s="23">
-        <f t="shared" ref="AC38" si="65">SUM(AC30:AC37)</f>
+        <f t="shared" ref="AC38" si="66">SUM(AC30:AC37)</f>
         <v>252.70000000000002</v>
       </c>
       <c r="AD38" s="23">
@@ -7782,7 +7875,9 @@
       <c r="T39" s="18">
         <v>183.67400000000001</v>
       </c>
-      <c r="U39" s="18"/>
+      <c r="U39" s="18">
+        <v>217.29400000000001</v>
+      </c>
       <c r="V39" s="18"/>
       <c r="W39" s="18"/>
       <c r="X39" s="18"/>
@@ -7875,7 +7970,9 @@
       <c r="T40" s="18">
         <v>107.15600000000001</v>
       </c>
-      <c r="U40" s="18"/>
+      <c r="U40" s="18">
+        <v>115.65300000000001</v>
+      </c>
       <c r="V40" s="18"/>
       <c r="W40" s="18"/>
       <c r="X40" s="18"/>
@@ -7968,7 +8065,9 @@
       <c r="T41" s="18">
         <v>29.55</v>
       </c>
-      <c r="U41" s="18"/>
+      <c r="U41" s="18">
+        <v>32.024000000000001</v>
+      </c>
       <c r="V41" s="18"/>
       <c r="W41" s="18"/>
       <c r="X41" s="18"/>
@@ -8061,7 +8160,9 @@
       <c r="T42" s="18">
         <v>279.66500000000002</v>
       </c>
-      <c r="U42" s="18"/>
+      <c r="U42" s="18">
+        <v>276.10599999999999</v>
+      </c>
       <c r="V42" s="18"/>
       <c r="W42" s="18"/>
       <c r="X42" s="18"/>
@@ -8104,95 +8205,98 @@
         <v>49</v>
       </c>
       <c r="D43" s="23">
-        <f t="shared" ref="D43:M43" si="66">SUM(D39:D42)</f>
+        <f t="shared" ref="D43:M43" si="67">SUM(D39:D42)</f>
         <v>673.62</v>
       </c>
       <c r="E43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>585.54999999999995</v>
       </c>
       <c r="F43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>673.5</v>
       </c>
       <c r="G43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>673.5</v>
       </c>
       <c r="H43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>554.274</v>
       </c>
       <c r="I43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>609</v>
       </c>
       <c r="J43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>565.34999999999991</v>
       </c>
       <c r="K43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>609</v>
       </c>
       <c r="L43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>551</v>
       </c>
       <c r="M43" s="23">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>558.04099999999994</v>
       </c>
       <c r="N43" s="23">
-        <f t="shared" ref="N43:T43" si="67">SUM(N39:N42)</f>
+        <f t="shared" ref="N43:T43" si="68">SUM(N39:N42)</f>
         <v>572.62</v>
       </c>
       <c r="O43" s="23">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>553.26199999999994</v>
       </c>
       <c r="P43" s="23">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>551.71600000000001</v>
       </c>
       <c r="Q43" s="23">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>566.57600000000002</v>
       </c>
       <c r="R43" s="23">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>568.45799999999997</v>
       </c>
       <c r="S43" s="23">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>582.84100000000001</v>
       </c>
       <c r="T43" s="23">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>600.04500000000007</v>
       </c>
-      <c r="U43" s="18"/>
+      <c r="U43" s="23">
+        <f t="shared" ref="U43" si="69">SUM(U39:U42)</f>
+        <v>641.077</v>
+      </c>
       <c r="V43" s="18"/>
       <c r="W43" s="18"/>
       <c r="X43" s="18"/>
       <c r="Y43" s="23">
-        <f t="shared" ref="Y43:AA43" si="68">SUM(Y39:Y42)</f>
+        <f t="shared" ref="Y43:AA43" si="70">SUM(Y39:Y42)</f>
         <v>219.59000000000003</v>
       </c>
       <c r="Z43" s="23">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>398.66600000000005</v>
       </c>
       <c r="AA43" s="23">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>481.404</v>
       </c>
       <c r="AB43" s="23">
-        <f t="shared" ref="AB43" si="69">SUM(AB39:AB42)</f>
+        <f t="shared" ref="AB43" si="71">SUM(AB39:AB42)</f>
         <v>673.5</v>
       </c>
       <c r="AC43" s="23">
-        <f t="shared" ref="AC43" si="70">SUM(AC39:AC42)</f>
+        <f t="shared" ref="AC43" si="72">SUM(AC39:AC42)</f>
         <v>609</v>
       </c>
       <c r="AD43" s="23">
@@ -8221,95 +8325,98 @@
         <v>50</v>
       </c>
       <c r="D44" s="16">
-        <f t="shared" ref="D44:M44" si="71">D43+D38</f>
+        <f t="shared" ref="D44:M44" si="73">D43+D38</f>
         <v>775.57</v>
       </c>
       <c r="E44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>686.09999999999991</v>
       </c>
       <c r="F44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>775.45</v>
       </c>
       <c r="G44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>775.45</v>
       </c>
       <c r="H44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>763.57400000000007</v>
       </c>
       <c r="I44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>861.7</v>
       </c>
       <c r="J44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>789.84999999999991</v>
       </c>
       <c r="K44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>861.7</v>
       </c>
       <c r="L44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>804</v>
       </c>
       <c r="M44" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>817.16199999999992</v>
       </c>
       <c r="N44" s="16">
-        <f t="shared" ref="N44:T44" si="72">N43+N38</f>
+        <f t="shared" ref="N44:T44" si="74">N43+N38</f>
         <v>831.62</v>
       </c>
       <c r="O44" s="16">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>806.70699999999988</v>
       </c>
       <c r="P44" s="16">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>804.34100000000001</v>
       </c>
       <c r="Q44" s="16">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>829.48700000000008</v>
       </c>
       <c r="R44" s="16">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>968.35899999999992</v>
       </c>
       <c r="S44" s="16">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>982.91700000000003</v>
       </c>
       <c r="T44" s="16">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1008.537</v>
       </c>
-      <c r="U44" s="18"/>
+      <c r="U44" s="16">
+        <f t="shared" ref="U44" si="75">U43+U38</f>
+        <v>1041.347</v>
+      </c>
       <c r="V44" s="18"/>
       <c r="W44" s="18"/>
       <c r="X44" s="18"/>
       <c r="Y44" s="16">
-        <f t="shared" ref="Y44:AA44" si="73">Y43+Y38</f>
+        <f t="shared" ref="Y44:AA44" si="76">Y43+Y38</f>
         <v>318.36</v>
       </c>
       <c r="Z44" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>502.95900000000006</v>
       </c>
       <c r="AA44" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>584.61400000000003</v>
       </c>
       <c r="AB44" s="16">
-        <f t="shared" ref="AB44" si="74">AB43+AB38</f>
+        <f t="shared" ref="AB44" si="77">AB43+AB38</f>
         <v>775.45</v>
       </c>
       <c r="AC44" s="16">
-        <f t="shared" ref="AC44" si="75">AC43+AC38</f>
+        <f t="shared" ref="AC44" si="78">AC43+AC38</f>
         <v>861.7</v>
       </c>
       <c r="AD44" s="16">
@@ -8388,7 +8495,9 @@
       <c r="T45" s="18">
         <v>0</v>
       </c>
-      <c r="U45" s="18"/>
+      <c r="U45" s="18">
+        <v>0.32400000000000001</v>
+      </c>
       <c r="V45" s="18"/>
       <c r="W45" s="18"/>
       <c r="X45" s="18"/>
@@ -8481,7 +8590,9 @@
       <c r="T46" s="18">
         <v>0</v>
       </c>
-      <c r="U46" s="18"/>
+      <c r="U46" s="18">
+        <v>0</v>
+      </c>
       <c r="V46" s="18"/>
       <c r="W46" s="18"/>
       <c r="X46" s="18"/>
@@ -8574,7 +8685,9 @@
       <c r="T47" s="18">
         <v>338.89699999999999</v>
       </c>
-      <c r="U47" s="18"/>
+      <c r="U47" s="18">
+        <v>338.89699999999999</v>
+      </c>
       <c r="V47" s="18"/>
       <c r="W47" s="18"/>
       <c r="X47" s="18"/>
@@ -8667,7 +8780,9 @@
       <c r="T48" s="18">
         <v>341.01299999999998</v>
       </c>
-      <c r="U48" s="18"/>
+      <c r="U48" s="18">
+        <v>363.76100000000002</v>
+      </c>
       <c r="V48" s="18"/>
       <c r="W48" s="18"/>
       <c r="X48" s="18"/>
@@ -8709,103 +8824,106 @@
       <c r="C49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="47">
-        <f t="shared" ref="D49:M49" si="76">SUM(D45:D48)</f>
+      <c r="D49" s="45">
+        <f t="shared" ref="D49:M49" si="79">SUM(D45:D48)</f>
         <v>583.14800000000002</v>
       </c>
-      <c r="E49" s="47">
-        <f t="shared" si="76"/>
+      <c r="E49" s="45">
+        <f t="shared" si="79"/>
         <v>523.28899999999999</v>
       </c>
-      <c r="F49" s="47">
-        <f t="shared" si="76"/>
+      <c r="F49" s="45">
+        <f t="shared" si="79"/>
         <v>583.1</v>
       </c>
-      <c r="G49" s="47">
-        <f t="shared" si="76"/>
+      <c r="G49" s="45">
+        <f t="shared" si="79"/>
         <v>583.22799999999995</v>
       </c>
-      <c r="H49" s="47">
-        <f t="shared" si="76"/>
+      <c r="H49" s="45">
+        <f t="shared" si="79"/>
         <v>591.64800000000002</v>
       </c>
-      <c r="I49" s="47">
-        <f t="shared" si="76"/>
+      <c r="I49" s="45">
+        <f t="shared" si="79"/>
         <v>601.74800000000005</v>
       </c>
-      <c r="J49" s="47">
-        <f t="shared" si="76"/>
+      <c r="J49" s="45">
+        <f t="shared" si="79"/>
         <v>611.548</v>
       </c>
-      <c r="K49" s="47">
-        <f t="shared" si="76"/>
+      <c r="K49" s="45">
+        <f t="shared" si="79"/>
         <v>601.74800000000005</v>
       </c>
-      <c r="L49" s="47">
-        <f t="shared" si="76"/>
+      <c r="L49" s="45">
+        <f t="shared" si="79"/>
         <v>558</v>
       </c>
-      <c r="M49" s="47">
-        <f t="shared" si="76"/>
+      <c r="M49" s="45">
+        <f t="shared" si="79"/>
         <v>561.97400000000005</v>
       </c>
-      <c r="N49" s="47">
-        <f t="shared" ref="N49:T49" si="77">SUM(N45:N48)</f>
+      <c r="N49" s="45">
+        <f t="shared" ref="N49:U49" si="80">SUM(N45:N48)</f>
         <v>573.79099999999994</v>
       </c>
-      <c r="O49" s="47">
-        <f t="shared" si="77"/>
+      <c r="O49" s="45">
+        <f t="shared" si="80"/>
         <v>569.76499999999999</v>
       </c>
-      <c r="P49" s="47">
-        <f t="shared" si="77"/>
+      <c r="P49" s="45">
+        <f t="shared" si="80"/>
         <v>559.15099999999995</v>
       </c>
-      <c r="Q49" s="47">
-        <f t="shared" si="77"/>
+      <c r="Q49" s="45">
+        <f t="shared" si="80"/>
         <v>575.452</v>
       </c>
-      <c r="R49" s="47">
-        <f t="shared" si="77"/>
+      <c r="R49" s="45">
+        <f t="shared" si="80"/>
         <v>671.88300000000004</v>
       </c>
-      <c r="S49" s="47">
-        <f t="shared" si="77"/>
+      <c r="S49" s="45">
+        <f t="shared" si="80"/>
         <v>679.58899999999994</v>
       </c>
-      <c r="T49" s="47">
-        <f t="shared" si="77"/>
+      <c r="T49" s="45">
+        <f t="shared" si="80"/>
         <v>679.91</v>
       </c>
-      <c r="U49" s="18"/>
+      <c r="U49" s="45">
+        <f t="shared" si="80"/>
+        <v>702.98199999999997</v>
+      </c>
       <c r="V49" s="18"/>
       <c r="W49" s="18"/>
       <c r="X49" s="18"/>
-      <c r="Y49" s="47">
-        <f t="shared" ref="Y49:AA49" si="78">SUM(Y45:Y48)</f>
+      <c r="Y49" s="45">
+        <f t="shared" ref="Y49:AA49" si="81">SUM(Y45:Y48)</f>
         <v>232.20400000000001</v>
       </c>
-      <c r="Z49" s="47">
-        <f t="shared" si="78"/>
+      <c r="Z49" s="45">
+        <f t="shared" si="81"/>
         <v>389.26600000000002</v>
       </c>
-      <c r="AA49" s="47">
-        <f t="shared" si="78"/>
+      <c r="AA49" s="45">
+        <f t="shared" si="81"/>
         <v>440.68900000000002</v>
       </c>
-      <c r="AB49" s="47">
-        <f t="shared" ref="AB49" si="79">SUM(AB45:AB48)</f>
+      <c r="AB49" s="45">
+        <f t="shared" ref="AB49" si="82">SUM(AB45:AB48)</f>
         <v>583.22799999999995</v>
       </c>
-      <c r="AC49" s="47">
-        <f t="shared" ref="AC49" si="80">SUM(AC45:AC48)</f>
+      <c r="AC49" s="45">
+        <f t="shared" ref="AC49" si="83">SUM(AC45:AC48)</f>
         <v>601.74800000000005</v>
       </c>
-      <c r="AD49" s="47">
+      <c r="AD49" s="45">
         <f>SUM(AD45:AD48)</f>
         <v>569.76499999999999</v>
       </c>
-      <c r="AE49" s="47">
+      <c r="AE49" s="45">
         <f>SUM(AE45:AE48)</f>
         <v>679.58899999999994</v>
       </c>
@@ -8877,7 +8995,9 @@
       <c r="T50" s="18">
         <v>0.92300000000000004</v>
       </c>
-      <c r="U50" s="18"/>
+      <c r="U50" s="18">
+        <v>0.878</v>
+      </c>
       <c r="V50" s="18"/>
       <c r="W50" s="18"/>
       <c r="X50" s="18"/>
@@ -8970,7 +9090,9 @@
       <c r="T51" s="18">
         <v>101.68</v>
       </c>
-      <c r="U51" s="18"/>
+      <c r="U51" s="18">
+        <v>99.888000000000005</v>
+      </c>
       <c r="V51" s="18"/>
       <c r="W51" s="18"/>
       <c r="X51" s="18"/>
@@ -9065,7 +9187,10 @@
         <f>8+52</f>
         <v>60</v>
       </c>
-      <c r="U52" s="18"/>
+      <c r="U52" s="18">
+        <f>8+49.28</f>
+        <v>57.28</v>
+      </c>
       <c r="V52" s="18"/>
       <c r="W52" s="18"/>
       <c r="X52" s="18"/>
@@ -9112,88 +9237,91 @@
         <v>14.299999999999999</v>
       </c>
       <c r="E53" s="23">
-        <f t="shared" ref="E53:M53" si="81">SUM(E50:E52)</f>
+        <f t="shared" ref="E53:M53" si="84">SUM(E50:E52)</f>
         <v>13.2</v>
       </c>
       <c r="F53" s="23">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>15.8</v>
       </c>
       <c r="G53" s="23">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>15.861000000000001</v>
       </c>
       <c r="H53" s="23">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>14.299999999999999</v>
       </c>
       <c r="I53" s="23">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>146.26400000000001</v>
       </c>
       <c r="J53" s="23">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>27.8</v>
       </c>
       <c r="K53" s="23">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>146.291</v>
       </c>
       <c r="L53" s="23">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>144</v>
       </c>
       <c r="M53" s="23">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>141.65</v>
       </c>
       <c r="N53" s="23">
-        <f t="shared" ref="N53:T53" si="82">SUM(N50:N52)</f>
+        <f t="shared" ref="N53:U53" si="85">SUM(N50:N52)</f>
         <v>142.73500000000001</v>
       </c>
       <c r="O53" s="23">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>133.85300000000001</v>
       </c>
       <c r="P53" s="23">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>142.97499999999999</v>
       </c>
       <c r="Q53" s="23">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>151.55099999999999</v>
       </c>
       <c r="R53" s="23">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>159.52199999999999</v>
       </c>
       <c r="S53" s="23">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>107.52199999999999</v>
       </c>
       <c r="T53" s="23">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>162.60300000000001</v>
       </c>
-      <c r="U53" s="18"/>
+      <c r="U53" s="23">
+        <f t="shared" si="85"/>
+        <v>158.04599999999999</v>
+      </c>
       <c r="V53" s="18"/>
       <c r="W53" s="18"/>
       <c r="X53" s="18"/>
       <c r="Y53" s="18"/>
       <c r="Z53" s="23">
-        <f t="shared" ref="Z53:AB53" si="83">SUM(Z50:Z52)</f>
+        <f t="shared" ref="Z53:AB53" si="86">SUM(Z50:Z52)</f>
         <v>18.786000000000001</v>
       </c>
       <c r="AA53" s="23">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>12.227</v>
       </c>
       <c r="AB53" s="23">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>15.861000000000001</v>
       </c>
       <c r="AC53" s="23">
-        <f t="shared" ref="AC53" si="84">SUM(AC50:AC52)</f>
+        <f t="shared" ref="AC53" si="87">SUM(AC50:AC52)</f>
         <v>146.291</v>
       </c>
       <c r="AD53" s="23">
@@ -9272,7 +9400,9 @@
       <c r="T54" s="18">
         <v>41.250999999999998</v>
       </c>
-      <c r="U54" s="18"/>
+      <c r="U54" s="18">
+        <v>60.734000000000002</v>
+      </c>
       <c r="V54" s="18"/>
       <c r="W54" s="18"/>
       <c r="X54" s="18"/>
@@ -9365,7 +9495,9 @@
       <c r="T55" s="18">
         <v>3</v>
       </c>
-      <c r="U55" s="18"/>
+      <c r="U55" s="18">
+        <v>2.4550000000000001</v>
+      </c>
       <c r="V55" s="18"/>
       <c r="W55" s="18"/>
       <c r="X55" s="18"/>
@@ -9458,7 +9590,9 @@
       <c r="T56" s="18">
         <v>9</v>
       </c>
-      <c r="U56" s="18"/>
+      <c r="U56" s="18">
+        <v>5.9320000000000004</v>
+      </c>
       <c r="V56" s="18"/>
       <c r="W56" s="18"/>
       <c r="X56" s="18"/>
@@ -9551,7 +9685,9 @@
       <c r="T57" s="18">
         <v>12.853</v>
       </c>
-      <c r="U57" s="18"/>
+      <c r="U57" s="18">
+        <v>12.366</v>
+      </c>
       <c r="V57" s="18"/>
       <c r="W57" s="18"/>
       <c r="X57" s="18"/>
@@ -9644,7 +9780,9 @@
       <c r="T58" s="18">
         <v>99.34</v>
       </c>
-      <c r="U58" s="18"/>
+      <c r="U58" s="18">
+        <v>98.911000000000001</v>
+      </c>
       <c r="V58" s="18"/>
       <c r="W58" s="18"/>
       <c r="X58" s="18"/>
@@ -9687,95 +9825,98 @@
         <v>65</v>
       </c>
       <c r="D59" s="23">
-        <f t="shared" ref="D59:M59" si="85">SUM(D54:D58)</f>
+        <f t="shared" ref="D59:M59" si="88">SUM(D54:D58)</f>
         <v>157.75</v>
       </c>
       <c r="E59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>149.69999999999999</v>
       </c>
       <c r="F59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>177.029</v>
       </c>
       <c r="G59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>177.02600000000001</v>
       </c>
       <c r="H59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>157.84</v>
       </c>
       <c r="I59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>113.9</v>
       </c>
       <c r="J59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>151.05000000000001</v>
       </c>
       <c r="K59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>113.9</v>
       </c>
       <c r="L59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>101</v>
       </c>
       <c r="M59" s="23">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>113.10000000000001</v>
       </c>
       <c r="N59" s="23">
-        <f t="shared" ref="N59:T59" si="86">SUM(N54:N58)</f>
+        <f t="shared" ref="N59:T59" si="89">SUM(N54:N58)</f>
         <v>115.09299999999999</v>
       </c>
       <c r="O59" s="23">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>103.086</v>
       </c>
       <c r="P59" s="23">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>101.404</v>
       </c>
       <c r="Q59" s="23">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>102.63</v>
       </c>
       <c r="R59" s="23">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>136.86099999999999</v>
       </c>
       <c r="S59" s="23">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>145.42099999999999</v>
       </c>
       <c r="T59" s="23">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>165.44400000000002</v>
       </c>
-      <c r="U59" s="18"/>
+      <c r="U59" s="23">
+        <f t="shared" ref="U59" si="90">SUM(U54:U58)</f>
+        <v>180.398</v>
+      </c>
       <c r="V59" s="18"/>
       <c r="W59" s="18"/>
       <c r="X59" s="18"/>
       <c r="Y59" s="23">
-        <f t="shared" ref="Y59:AA59" si="87">SUM(Y54:Y58)</f>
+        <f t="shared" ref="Y59:AA59" si="91">SUM(Y54:Y58)</f>
         <v>65.957999999999998</v>
       </c>
       <c r="Z59" s="23">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>94.908000000000001</v>
       </c>
       <c r="AA59" s="23">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>131.70400000000001</v>
       </c>
       <c r="AB59" s="23">
-        <f t="shared" ref="AB59" si="88">SUM(AB54:AB58)</f>
+        <f t="shared" ref="AB59" si="92">SUM(AB54:AB58)</f>
         <v>177.02600000000001</v>
       </c>
       <c r="AC59" s="23">
-        <f t="shared" ref="AC59" si="89">SUM(AC54:AC58)</f>
+        <f t="shared" ref="AC59" si="93">SUM(AC54:AC58)</f>
         <v>113.9</v>
       </c>
       <c r="AD59" s="23">
@@ -9804,95 +9945,98 @@
         <v>66</v>
       </c>
       <c r="D60" s="16">
-        <f t="shared" ref="D60:M60" si="90">D53+D59</f>
+        <f t="shared" ref="D60:M60" si="94">D53+D59</f>
         <v>172.05</v>
       </c>
       <c r="E60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>162.89999999999998</v>
       </c>
       <c r="F60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>192.82900000000001</v>
       </c>
       <c r="G60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>192.887</v>
       </c>
       <c r="H60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>172.14000000000001</v>
       </c>
       <c r="I60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>260.16399999999999</v>
       </c>
       <c r="J60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>178.85000000000002</v>
       </c>
       <c r="K60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>260.19100000000003</v>
       </c>
       <c r="L60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>245</v>
       </c>
       <c r="M60" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>254.75</v>
       </c>
       <c r="N60" s="16">
-        <f t="shared" ref="N60:T60" si="91">N53+N59</f>
+        <f t="shared" ref="N60:T60" si="95">N53+N59</f>
         <v>257.82799999999997</v>
       </c>
       <c r="O60" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>236.93900000000002</v>
       </c>
       <c r="P60" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>244.37899999999999</v>
       </c>
       <c r="Q60" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>254.18099999999998</v>
       </c>
       <c r="R60" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>296.38299999999998</v>
       </c>
       <c r="S60" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>252.94299999999998</v>
       </c>
       <c r="T60" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>328.04700000000003</v>
       </c>
-      <c r="U60" s="18"/>
+      <c r="U60" s="16">
+        <f t="shared" ref="U60" si="96">U53+U59</f>
+        <v>338.44399999999996</v>
+      </c>
       <c r="V60" s="18"/>
       <c r="W60" s="18"/>
       <c r="X60" s="18"/>
       <c r="Y60" s="16">
-        <f t="shared" ref="Y60:AA60" si="92">Y53+Y59</f>
+        <f t="shared" ref="Y60:AA60" si="97">Y53+Y59</f>
         <v>65.957999999999998</v>
       </c>
       <c r="Z60" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>113.694</v>
       </c>
       <c r="AA60" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>143.93100000000001</v>
       </c>
       <c r="AB60" s="16">
-        <f t="shared" ref="AB60" si="93">AB53+AB59</f>
+        <f t="shared" ref="AB60" si="98">AB53+AB59</f>
         <v>192.887</v>
       </c>
       <c r="AC60" s="16">
-        <f t="shared" ref="AC60" si="94">AC53+AC59</f>
+        <f t="shared" ref="AC60" si="99">AC53+AC59</f>
         <v>260.19100000000003</v>
       </c>
       <c r="AD60" s="16">
@@ -9921,95 +10065,98 @@
         <v>67</v>
       </c>
       <c r="D61" s="16">
-        <f t="shared" ref="D61:M61" si="95">D49+D60</f>
+        <f t="shared" ref="D61:M61" si="100">D49+D60</f>
         <v>755.19800000000009</v>
       </c>
       <c r="E61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>686.18899999999996</v>
       </c>
       <c r="F61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>775.92900000000009</v>
       </c>
       <c r="G61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>776.11500000000001</v>
       </c>
       <c r="H61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>763.78800000000001</v>
       </c>
       <c r="I61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>861.91200000000003</v>
       </c>
       <c r="J61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>790.39800000000002</v>
       </c>
       <c r="K61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>861.93900000000008</v>
       </c>
       <c r="L61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>803</v>
       </c>
       <c r="M61" s="16">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>816.72400000000005</v>
       </c>
       <c r="N61" s="16">
-        <f t="shared" ref="N61:T61" si="96">N49+N60</f>
+        <f t="shared" ref="N61:T61" si="101">N49+N60</f>
         <v>831.61899999999991</v>
       </c>
       <c r="O61" s="16">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>806.70399999999995</v>
       </c>
       <c r="P61" s="16">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>803.53</v>
       </c>
       <c r="Q61" s="16">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>829.63300000000004</v>
       </c>
       <c r="R61" s="16">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>968.26600000000008</v>
       </c>
       <c r="S61" s="16">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>932.53199999999993</v>
       </c>
       <c r="T61" s="16">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>1007.957</v>
       </c>
-      <c r="U61" s="18"/>
+      <c r="U61" s="16">
+        <f t="shared" ref="U61" si="102">U49+U60</f>
+        <v>1041.4259999999999</v>
+      </c>
       <c r="V61" s="18"/>
       <c r="W61" s="18"/>
       <c r="X61" s="18"/>
       <c r="Y61" s="16">
-        <f t="shared" ref="Y61:AA61" si="97">Y49+Y60</f>
+        <f t="shared" ref="Y61:AA61" si="103">Y49+Y60</f>
         <v>298.16200000000003</v>
       </c>
       <c r="Z61" s="16">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>502.96000000000004</v>
       </c>
       <c r="AA61" s="16">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>584.62</v>
       </c>
       <c r="AB61" s="16">
-        <f t="shared" ref="AB61" si="98">AB49+AB60</f>
+        <f t="shared" ref="AB61" si="104">AB49+AB60</f>
         <v>776.11500000000001</v>
       </c>
       <c r="AC61" s="16">
-        <f t="shared" ref="AC61" si="99">AC49+AC60</f>
+        <f t="shared" ref="AC61" si="105">AC49+AC60</f>
         <v>861.93900000000008</v>
       </c>
       <c r="AD61" s="16">
@@ -10075,51 +10222,51 @@
         <v>96</v>
       </c>
       <c r="D64" s="18">
-        <f t="shared" ref="D64:O64" si="100">D15</f>
+        <f t="shared" ref="D64:O64" si="106">D15</f>
         <v>44.449000000000012</v>
       </c>
       <c r="E64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>46.649000000000022</v>
       </c>
       <c r="F64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>51.274999999999991</v>
       </c>
       <c r="G64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>24.783999999999992</v>
       </c>
       <c r="H64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>8.3940000000000001</v>
       </c>
       <c r="I64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>19.580000000000016</v>
       </c>
       <c r="J64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>1.7050000000000036</v>
       </c>
       <c r="K64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>-17.583000000000002</v>
       </c>
       <c r="L64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>-30.633999999999993</v>
       </c>
       <c r="M64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>-17.977999999999998</v>
       </c>
       <c r="N64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>5.501000000000003</v>
       </c>
       <c r="O64" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="106"/>
         <v>-7.6000000000021828E-2</v>
       </c>
       <c r="P64" s="18">
@@ -10131,35 +10278,39 @@
         <v>10.071999999999999</v>
       </c>
       <c r="R64" s="18">
-        <f t="shared" ref="R64:T64" si="101">R15</f>
+        <f t="shared" ref="R64:U64" si="107">R15</f>
         <v>0.86400000000000343</v>
       </c>
       <c r="S64" s="18">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>0.19799999999998308</v>
       </c>
       <c r="T64" s="18">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>9.5770000000000159</v>
       </c>
+      <c r="U64" s="18">
+        <f t="shared" si="107"/>
+        <v>21.670000000000012</v>
+      </c>
       <c r="Y64" s="18">
-        <f t="shared" ref="Y64:AC64" si="102">Y15</f>
+        <f t="shared" ref="Y64:AC64" si="108">Y15</f>
         <v>10.048999999999985</v>
       </c>
       <c r="Z64" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="108"/>
         <v>43.587999999999994</v>
       </c>
       <c r="AA64" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="108"/>
         <v>87.830999999999989</v>
       </c>
       <c r="AB64" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="108"/>
         <v>167.15700000000001</v>
       </c>
       <c r="AC64" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="108"/>
         <v>12.09600000000006</v>
       </c>
       <c r="AD64" s="18">
@@ -10229,6 +10380,9 @@
       <c r="T65" s="18">
         <v>10</v>
       </c>
+      <c r="U65" s="18">
+        <v>21.649000000000001</v>
+      </c>
       <c r="Y65" s="18">
         <v>10</v>
       </c>
@@ -10309,6 +10463,9 @@
       <c r="T66" s="18">
         <v>-0.79900000000000004</v>
       </c>
+      <c r="U66" s="18">
+        <v>-2</v>
+      </c>
       <c r="Y66" s="18">
         <v>-4.8</v>
       </c>
@@ -10389,6 +10546,9 @@
       <c r="T67" s="18">
         <v>11</v>
       </c>
+      <c r="U67" s="18">
+        <v>11.36</v>
+      </c>
       <c r="Y67" s="18">
         <v>23.5</v>
       </c>
@@ -10469,6 +10629,9 @@
       <c r="T68" s="18">
         <v>1.1950000000000001</v>
       </c>
+      <c r="U68" s="18">
+        <v>0.64359999999999995</v>
+      </c>
       <c r="Y68" s="18">
         <v>0</v>
       </c>
@@ -10549,6 +10712,9 @@
       <c r="T69" s="18">
         <v>1.9330000000000001</v>
       </c>
+      <c r="U69" s="18">
+        <v>2.2650000000000001</v>
+      </c>
       <c r="Y69" s="18">
         <v>0</v>
       </c>
@@ -10629,6 +10795,9 @@
       <c r="T70" s="18">
         <v>-42.326000000000001</v>
       </c>
+      <c r="U70" s="18">
+        <v>-22.632999999999999</v>
+      </c>
       <c r="Y70" s="18">
         <v>-13.789</v>
       </c>
@@ -10709,6 +10878,9 @@
       <c r="T71" s="18">
         <v>4.9000000000000004</v>
       </c>
+      <c r="U71" s="18">
+        <v>5.5709999999999997</v>
+      </c>
       <c r="Y71" s="18">
         <v>1.1000000000000001</v>
       </c>
@@ -10794,6 +10966,9 @@
       <c r="T72" s="18">
         <v>15.241</v>
       </c>
+      <c r="U72" s="18">
+        <v>-1.3819999999999999</v>
+      </c>
       <c r="Y72" s="18">
         <v>3.9</v>
       </c>
@@ -10829,51 +11004,51 @@
         <v>68</v>
       </c>
       <c r="D73" s="16">
-        <f t="shared" ref="D73:O73" si="103">SUM(D65:D72)</f>
+        <f t="shared" ref="D73:O73" si="109">SUM(D65:D72)</f>
         <v>31.5</v>
       </c>
       <c r="E73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>30.199999999999996</v>
       </c>
       <c r="F73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>44.85</v>
       </c>
       <c r="G73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>36.200000000000003</v>
       </c>
       <c r="H73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>-130.19999999999999</v>
       </c>
       <c r="I73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>32.4</v>
       </c>
       <c r="J73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>-12.845000000000002</v>
       </c>
       <c r="K73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>-9.5999999999999979</v>
       </c>
       <c r="L73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>-34.799999999999997</v>
       </c>
       <c r="M73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>33.000000000000007</v>
       </c>
       <c r="N73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>13.900000000000002</v>
       </c>
       <c r="O73" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="109"/>
         <v>48.699999999999996</v>
       </c>
       <c r="P73" s="16">
@@ -10885,35 +11060,39 @@
         <v>46.68</v>
       </c>
       <c r="R73" s="16">
-        <f t="shared" ref="R73:T73" si="104">SUM(R65:R72)</f>
+        <f t="shared" ref="R73:U73" si="110">SUM(R65:R72)</f>
         <v>21.63</v>
       </c>
       <c r="S73" s="16">
-        <f t="shared" si="104"/>
+        <f t="shared" si="110"/>
         <v>13.834000000000001</v>
       </c>
       <c r="T73" s="16">
-        <f t="shared" si="104"/>
+        <f t="shared" si="110"/>
         <v>1.1440000000000001</v>
       </c>
+      <c r="U73" s="16">
+        <f t="shared" si="110"/>
+        <v>15.473600000000003</v>
+      </c>
       <c r="Y73" s="16">
-        <f t="shared" ref="Y73:AC73" si="105">SUM(Y65:Y72)</f>
+        <f t="shared" ref="Y73:AC73" si="111">SUM(Y65:Y72)</f>
         <v>19.910999999999998</v>
       </c>
       <c r="Z73" s="16">
-        <f t="shared" si="105"/>
+        <f t="shared" si="111"/>
         <v>65.150000000000006</v>
       </c>
       <c r="AA73" s="16">
-        <f t="shared" si="105"/>
+        <f t="shared" si="111"/>
         <v>95.628</v>
       </c>
       <c r="AB73" s="16">
-        <f t="shared" si="105"/>
+        <f t="shared" si="111"/>
         <v>142.25</v>
       </c>
       <c r="AC73" s="16">
-        <f t="shared" si="105"/>
+        <f t="shared" si="111"/>
         <v>-119</v>
       </c>
       <c r="AD73" s="16">
@@ -10992,6 +11171,9 @@
       <c r="T75" s="18">
         <v>-9.2260000000000009</v>
       </c>
+      <c r="U75" s="18">
+        <v>-8.2710000000000008</v>
+      </c>
       <c r="Y75" s="18">
         <v>-20</v>
       </c>
@@ -11072,6 +11254,9 @@
       <c r="T76" s="18">
         <v>-3.3809999999999998</v>
       </c>
+      <c r="U76" s="18">
+        <v>-2.738</v>
+      </c>
       <c r="Y76" s="18">
         <v>-11</v>
       </c>
@@ -11152,6 +11337,9 @@
       <c r="T77" s="18">
         <v>0</v>
       </c>
+      <c r="U77" s="18">
+        <v>0</v>
+      </c>
       <c r="Y77" s="18">
         <v>0</v>
       </c>
@@ -11177,7 +11365,61 @@
       <c r="A78" s="1"/>
       <c r="B78" s="5"/>
       <c r="C78" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
+      </c>
+      <c r="D78" s="18">
+        <v>0</v>
+      </c>
+      <c r="E78" s="18">
+        <v>0</v>
+      </c>
+      <c r="F78" s="18">
+        <v>0</v>
+      </c>
+      <c r="G78" s="18">
+        <v>0</v>
+      </c>
+      <c r="H78" s="18">
+        <v>0</v>
+      </c>
+      <c r="I78" s="18">
+        <v>0</v>
+      </c>
+      <c r="J78" s="18">
+        <v>0</v>
+      </c>
+      <c r="K78" s="18">
+        <v>0</v>
+      </c>
+      <c r="L78" s="18">
+        <v>0</v>
+      </c>
+      <c r="M78" s="18">
+        <v>0</v>
+      </c>
+      <c r="N78" s="18">
+        <v>0</v>
+      </c>
+      <c r="O78" s="18">
+        <v>0</v>
+      </c>
+      <c r="P78" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="18">
+        <v>0</v>
+      </c>
+      <c r="R78" s="18">
+        <v>0</v>
+      </c>
+      <c r="S78" s="18">
+        <v>0</v>
+      </c>
+      <c r="T78" s="18">
+        <v>0</v>
+      </c>
+      <c r="U78" s="18">
+        <v>0</v>
       </c>
       <c r="AE78" s="18">
         <v>-0.51900000000000002</v>
@@ -11188,7 +11430,61 @@
       <c r="A79" s="1"/>
       <c r="B79" s="5"/>
       <c r="C79" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
+      </c>
+      <c r="D79" s="18">
+        <v>0</v>
+      </c>
+      <c r="E79" s="18">
+        <v>0</v>
+      </c>
+      <c r="F79" s="18">
+        <v>0</v>
+      </c>
+      <c r="G79" s="18">
+        <v>0</v>
+      </c>
+      <c r="H79" s="18">
+        <v>0</v>
+      </c>
+      <c r="I79" s="18">
+        <v>0</v>
+      </c>
+      <c r="J79" s="18">
+        <v>0</v>
+      </c>
+      <c r="K79" s="18">
+        <v>0</v>
+      </c>
+      <c r="L79" s="18">
+        <v>0</v>
+      </c>
+      <c r="M79" s="18">
+        <v>0</v>
+      </c>
+      <c r="N79" s="18">
+        <v>0</v>
+      </c>
+      <c r="O79" s="18">
+        <v>0</v>
+      </c>
+      <c r="P79" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="18">
+        <v>0</v>
+      </c>
+      <c r="R79" s="18">
+        <v>0</v>
+      </c>
+      <c r="S79" s="18">
+        <v>0</v>
+      </c>
+      <c r="T79" s="18">
+        <v>0</v>
+      </c>
+      <c r="U79" s="18">
+        <v>0</v>
       </c>
       <c r="AE79" s="18">
         <v>-111.663</v>
@@ -11199,7 +11495,61 @@
       <c r="A80" s="1"/>
       <c r="B80" s="5"/>
       <c r="C80" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
+      </c>
+      <c r="D80" s="18">
+        <v>0</v>
+      </c>
+      <c r="E80" s="18">
+        <v>0</v>
+      </c>
+      <c r="F80" s="18">
+        <v>0</v>
+      </c>
+      <c r="G80" s="18">
+        <v>0</v>
+      </c>
+      <c r="H80" s="18">
+        <v>0</v>
+      </c>
+      <c r="I80" s="18">
+        <v>0</v>
+      </c>
+      <c r="J80" s="18">
+        <v>0</v>
+      </c>
+      <c r="K80" s="18">
+        <v>0</v>
+      </c>
+      <c r="L80" s="18">
+        <v>0</v>
+      </c>
+      <c r="M80" s="18">
+        <v>0</v>
+      </c>
+      <c r="N80" s="18">
+        <v>0</v>
+      </c>
+      <c r="O80" s="18">
+        <v>0</v>
+      </c>
+      <c r="P80" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="18">
+        <v>0</v>
+      </c>
+      <c r="R80" s="18">
+        <v>0</v>
+      </c>
+      <c r="S80" s="18">
+        <v>0</v>
+      </c>
+      <c r="T80" s="18">
+        <v>0</v>
+      </c>
+      <c r="U80" s="18">
+        <v>0</v>
       </c>
       <c r="AE80" s="18">
         <v>18.893000000000001</v>
@@ -11213,35 +11563,35 @@
         <v>69</v>
       </c>
       <c r="D81" s="16">
-        <f t="shared" ref="D81:O81" si="106">SUM(D75:D77)</f>
+        <f t="shared" ref="D81:O81" si="112">SUM(D75:D77)</f>
         <v>-5.6999999999999993</v>
       </c>
       <c r="E81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-6</v>
       </c>
       <c r="F81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-9</v>
       </c>
       <c r="G81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-9.3000000000000007</v>
       </c>
       <c r="H81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-14.6</v>
       </c>
       <c r="I81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-11.16</v>
       </c>
       <c r="J81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-7.6</v>
       </c>
       <c r="K81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-19.826999999999998</v>
       </c>
       <c r="L81" s="16">
@@ -11249,15 +11599,15 @@
         <v>-5.1000000000000005</v>
       </c>
       <c r="M81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-5.4</v>
       </c>
       <c r="N81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-7.4</v>
       </c>
       <c r="O81" s="16">
-        <f t="shared" si="106"/>
+        <f t="shared" si="112"/>
         <v>-10.5</v>
       </c>
       <c r="P81" s="16">
@@ -11269,35 +11619,39 @@
         <v>-13.205</v>
       </c>
       <c r="R81" s="16">
-        <f t="shared" ref="R81:T81" si="107">SUM(R75:R77)</f>
+        <f t="shared" ref="R81:T81" si="113">SUM(R75:R77)</f>
         <v>-134.54599999999999</v>
       </c>
       <c r="S81" s="16">
-        <f t="shared" si="107"/>
+        <f t="shared" si="113"/>
         <v>-10.975999999999999</v>
       </c>
       <c r="T81" s="16">
-        <f t="shared" si="107"/>
+        <f t="shared" si="113"/>
         <v>-12.607000000000001</v>
       </c>
+      <c r="U81" s="16">
+        <f>SUM(U75:U80)</f>
+        <v>-11.009</v>
+      </c>
       <c r="Y81" s="16">
-        <f t="shared" ref="Y81:AC81" si="108">SUM(Y75:Y77)</f>
+        <f t="shared" ref="Y81:AC81" si="114">SUM(Y75:Y77)</f>
         <v>-31</v>
       </c>
       <c r="Z81" s="16">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>-37.78</v>
       </c>
       <c r="AA81" s="16">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>-30.6</v>
       </c>
       <c r="AB81" s="16">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>-30.4</v>
       </c>
       <c r="AC81" s="16">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>-53.4</v>
       </c>
       <c r="AD81" s="16">
@@ -11374,6 +11728,9 @@
       <c r="T83" s="18">
         <v>-13.743</v>
       </c>
+      <c r="U83" s="18">
+        <v>0</v>
+      </c>
       <c r="Y83" s="18">
         <v>2.4119999999999999</v>
       </c>
@@ -11451,6 +11808,9 @@
       <c r="T84" s="18">
         <v>0</v>
       </c>
+      <c r="U84" s="18">
+        <v>0</v>
+      </c>
       <c r="Y84" s="18">
         <v>0</v>
       </c>
@@ -11519,6 +11879,9 @@
       <c r="T85" s="18">
         <v>-1.9279999999999999</v>
       </c>
+      <c r="U85" s="18">
+        <v>-1.913</v>
+      </c>
       <c r="Y85" s="18">
         <v>0</v>
       </c>
@@ -11599,6 +11962,9 @@
       <c r="T86" s="18">
         <v>-2.3690000000000002</v>
       </c>
+      <c r="U86" s="18">
+        <v>-2.5259999999999998</v>
+      </c>
       <c r="Y86" s="18">
         <v>-3.9</v>
       </c>
@@ -11679,6 +12045,9 @@
       <c r="T87" s="18">
         <v>-1</v>
       </c>
+      <c r="U87" s="18">
+        <v>-0.99199999999999999</v>
+      </c>
       <c r="Y87" s="18">
         <v>0</v>
       </c>
@@ -11706,7 +12075,61 @@
       <c r="A88" s="1"/>
       <c r="B88" s="5"/>
       <c r="C88" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
+      </c>
+      <c r="D88" s="18">
+        <v>0</v>
+      </c>
+      <c r="E88" s="18">
+        <v>0</v>
+      </c>
+      <c r="F88" s="18">
+        <v>0</v>
+      </c>
+      <c r="G88" s="18">
+        <v>0</v>
+      </c>
+      <c r="H88" s="18">
+        <v>0</v>
+      </c>
+      <c r="I88" s="18">
+        <v>0</v>
+      </c>
+      <c r="J88" s="18">
+        <v>0</v>
+      </c>
+      <c r="K88" s="18">
+        <v>0</v>
+      </c>
+      <c r="L88" s="18">
+        <v>0</v>
+      </c>
+      <c r="M88" s="18">
+        <v>0</v>
+      </c>
+      <c r="N88" s="18">
+        <v>0</v>
+      </c>
+      <c r="O88" s="18">
+        <v>0</v>
+      </c>
+      <c r="P88" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="18">
+        <v>0</v>
+      </c>
+      <c r="R88" s="18">
+        <v>0</v>
+      </c>
+      <c r="S88" s="18">
+        <v>0</v>
+      </c>
+      <c r="T88" s="18">
+        <v>0</v>
+      </c>
+      <c r="U88" s="18">
+        <v>0</v>
       </c>
       <c r="AE88" s="18">
         <v>100</v>
@@ -11717,7 +12140,61 @@
       <c r="A89" s="1"/>
       <c r="B89" s="5"/>
       <c r="C89" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
+      </c>
+      <c r="D89" s="18">
+        <v>0</v>
+      </c>
+      <c r="E89" s="18">
+        <v>0</v>
+      </c>
+      <c r="F89" s="18">
+        <v>0</v>
+      </c>
+      <c r="G89" s="18">
+        <v>0</v>
+      </c>
+      <c r="H89" s="18">
+        <v>0</v>
+      </c>
+      <c r="I89" s="18">
+        <v>0</v>
+      </c>
+      <c r="J89" s="18">
+        <v>0</v>
+      </c>
+      <c r="K89" s="18">
+        <v>0</v>
+      </c>
+      <c r="L89" s="18">
+        <v>0</v>
+      </c>
+      <c r="M89" s="18">
+        <v>0</v>
+      </c>
+      <c r="N89" s="18">
+        <v>0</v>
+      </c>
+      <c r="O89" s="18">
+        <v>0</v>
+      </c>
+      <c r="P89" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="18">
+        <v>0</v>
+      </c>
+      <c r="R89" s="18">
+        <v>0</v>
+      </c>
+      <c r="S89" s="18">
+        <v>0</v>
+      </c>
+      <c r="T89" s="18">
+        <v>0</v>
+      </c>
+      <c r="U89" s="18">
+        <v>0</v>
       </c>
       <c r="AE89" s="18">
         <v>-100</v>
@@ -11782,6 +12259,9 @@
       <c r="T90" s="18">
         <v>-0.217</v>
       </c>
+      <c r="U90" s="18">
+        <v>-0.2</v>
+      </c>
       <c r="Y90" s="18">
         <v>0</v>
       </c>
@@ -11813,95 +12293,99 @@
         <v>70</v>
       </c>
       <c r="D91" s="16">
-        <f t="shared" ref="D91:T91" si="109">SUM(D83:D90)</f>
+        <f t="shared" ref="D91:U91" si="115">SUM(D83:D90)</f>
         <v>-1.5</v>
       </c>
       <c r="E91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-6.2</v>
       </c>
       <c r="F91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-1.4</v>
       </c>
       <c r="G91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-2</v>
       </c>
       <c r="H91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-1.8</v>
       </c>
       <c r="I91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-1.9</v>
       </c>
       <c r="J91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-2.1</v>
       </c>
       <c r="K91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>90.5</v>
       </c>
       <c r="L91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-8.5039999999999996</v>
       </c>
       <c r="M91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-4.5</v>
       </c>
       <c r="N91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-4.6950000000000003</v>
       </c>
       <c r="O91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-4.4000000000000004</v>
       </c>
       <c r="P91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-21.241</v>
       </c>
       <c r="Q91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-5.0529999999999999</v>
       </c>
       <c r="R91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>83.25800000000001</v>
       </c>
       <c r="S91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-5.3059999999999992</v>
       </c>
       <c r="T91" s="16">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>-19.256999999999998</v>
       </c>
+      <c r="U91" s="16">
+        <f t="shared" si="115"/>
+        <v>-5.6310000000000002</v>
+      </c>
       <c r="Y91" s="16">
-        <f t="shared" ref="Y91:AD91" si="110">SUM(Y83:Y90)</f>
+        <f t="shared" ref="Y91:AD91" si="116">SUM(Y83:Y90)</f>
         <v>-1.488</v>
       </c>
       <c r="Z91" s="16">
-        <f t="shared" si="110"/>
+        <f t="shared" si="116"/>
         <v>123.727</v>
       </c>
       <c r="AA91" s="16">
-        <f t="shared" si="110"/>
+        <f t="shared" si="116"/>
         <v>-27.158000000000001</v>
       </c>
       <c r="AB91" s="16">
-        <f t="shared" si="110"/>
+        <f t="shared" si="116"/>
         <v>-11.3</v>
       </c>
       <c r="AC91" s="16">
-        <f t="shared" si="110"/>
+        <f t="shared" si="116"/>
         <v>83.789000000000001</v>
       </c>
       <c r="AD91" s="16">
-        <f t="shared" si="110"/>
+        <f t="shared" si="116"/>
         <v>-23</v>
       </c>
       <c r="AE91" s="16">
@@ -11974,6 +12458,9 @@
       <c r="T93" s="18">
         <v>3.2450000000000001</v>
       </c>
+      <c r="U93" s="18">
+        <v>-2.2229999999999999</v>
+      </c>
       <c r="Y93" s="18">
         <v>0</v>
       </c>
@@ -12011,98 +12498,102 @@
         <v>113</v>
       </c>
       <c r="D95" s="18">
-        <f t="shared" ref="D95:P95" si="111">D73+D81+D91+D93</f>
+        <f t="shared" ref="D95:P95" si="117">D73+D81+D91+D93</f>
         <v>23.865000000000002</v>
       </c>
       <c r="E95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>16.999999999999996</v>
       </c>
       <c r="F95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>33.450000000000003</v>
       </c>
       <c r="G95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>26.46</v>
       </c>
       <c r="H95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>-146.6</v>
       </c>
       <c r="I95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>19.34</v>
       </c>
       <c r="J95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>-23.150000000000002</v>
       </c>
       <c r="K95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>61.973000000000006</v>
       </c>
       <c r="L95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>-54.403999999999996</v>
       </c>
       <c r="M95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>23.693000000000008</v>
       </c>
       <c r="N95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>3.2050000000000014</v>
       </c>
       <c r="O95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>33.799999999999997</v>
       </c>
       <c r="P95" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="117"/>
         <v>19.573999999999998</v>
       </c>
       <c r="Q95" s="18">
-        <f t="shared" ref="Q95:S95" si="112">Q73+Q81+Q91+Q93</f>
+        <f t="shared" ref="Q95:S95" si="118">Q73+Q81+Q91+Q93</f>
         <v>27.922000000000001</v>
       </c>
       <c r="R95" s="18">
-        <f t="shared" si="112"/>
+        <f t="shared" si="118"/>
         <v>-25.657999999999987</v>
       </c>
       <c r="S95" s="18">
-        <f t="shared" si="112"/>
+        <f t="shared" si="118"/>
         <v>-3.9479999999999968</v>
       </c>
       <c r="T95" s="18">
-        <f t="shared" ref="T95" si="113">T73+T81+T91+T93</f>
+        <f t="shared" ref="T95:U95" si="119">T73+T81+T91+T93</f>
         <v>-27.474999999999998</v>
       </c>
+      <c r="U95" s="18">
+        <f t="shared" si="119"/>
+        <v>-3.3893999999999975</v>
+      </c>
       <c r="Y95" s="18">
-        <f t="shared" ref="Y95:AD95" si="114">Y73+Y81+Y91+Y93</f>
+        <f t="shared" ref="Y95:AD95" si="120">Y73+Y81+Y91+Y93</f>
         <v>-12.577000000000002</v>
       </c>
       <c r="Z95" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="120"/>
         <v>152.09700000000001</v>
       </c>
       <c r="AA95" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="120"/>
         <v>36.86999999999999</v>
       </c>
       <c r="AB95" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="120"/>
         <v>99.55</v>
       </c>
       <c r="AC95" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="120"/>
         <v>-87.981000000000009</v>
       </c>
       <c r="AD95" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="120"/>
         <v>-2.4749999999999961</v>
       </c>
-      <c r="AE95" s="72">
+      <c r="AE95" s="70">
         <f>AE73+AE81+AE91+AE93</f>
         <v>15.144999999999971</v>
       </c>
@@ -12122,35 +12613,35 @@
         <v>114</v>
       </c>
       <c r="D97" s="18">
-        <f t="shared" ref="D97:O97" si="115">D73+D81</f>
+        <f t="shared" ref="D97:O97" si="121">D73+D81</f>
         <v>25.8</v>
       </c>
       <c r="E97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>24.199999999999996</v>
       </c>
       <c r="F97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>35.85</v>
       </c>
       <c r="G97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>26.900000000000002</v>
       </c>
       <c r="H97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>-144.79999999999998</v>
       </c>
       <c r="I97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>21.24</v>
       </c>
       <c r="J97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>-20.445</v>
       </c>
       <c r="K97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>-29.426999999999996</v>
       </c>
       <c r="L97" s="18">
@@ -12158,15 +12649,15 @@
         <v>-39.9</v>
       </c>
       <c r="M97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>27.600000000000009</v>
       </c>
       <c r="N97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>6.5000000000000018</v>
       </c>
       <c r="O97" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>38.199999999999996</v>
       </c>
       <c r="P97" s="18">
@@ -12178,42 +12669,46 @@
         <v>33.475000000000001</v>
       </c>
       <c r="R97" s="18">
-        <f t="shared" ref="R97:S97" si="116">R73+R81</f>
+        <f t="shared" ref="R97:S97" si="122">R73+R81</f>
         <v>-112.916</v>
       </c>
       <c r="S97" s="18">
-        <f t="shared" si="116"/>
+        <f t="shared" si="122"/>
         <v>2.8580000000000023</v>
       </c>
       <c r="T97" s="18">
-        <f t="shared" ref="T97" si="117">T73+T81</f>
+        <f t="shared" ref="T97:U97" si="123">T73+T81</f>
         <v>-11.463000000000001</v>
       </c>
+      <c r="U97" s="18">
+        <f t="shared" si="123"/>
+        <v>4.4646000000000026</v>
+      </c>
       <c r="Y97" s="18">
-        <f t="shared" ref="Y97:AC97" si="118">Y73+Y81</f>
+        <f t="shared" ref="Y97:AC97" si="124">Y73+Y81</f>
         <v>-11.089000000000002</v>
       </c>
       <c r="Z97" s="18">
-        <f t="shared" si="118"/>
+        <f t="shared" si="124"/>
         <v>27.370000000000005</v>
       </c>
       <c r="AA97" s="18">
-        <f t="shared" si="118"/>
+        <f t="shared" si="124"/>
         <v>65.027999999999992</v>
       </c>
       <c r="AB97" s="18">
-        <f t="shared" si="118"/>
+        <f t="shared" si="124"/>
         <v>111.85</v>
       </c>
       <c r="AC97" s="18">
-        <f t="shared" si="118"/>
+        <f t="shared" si="124"/>
         <v>-172.4</v>
       </c>
       <c r="AD97" s="18">
         <f>AD73+AD81</f>
         <v>31.175000000000004</v>
       </c>
-      <c r="AE97" s="72">
+      <c r="AE97" s="70">
         <f>AE73+AE81</f>
         <v>-50.986000000000018</v>
       </c>
@@ -12554,109 +13049,109 @@
       <c r="B3" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="35">
         <v>2022</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="K3" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="35">
         <v>2023</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="M3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="35" t="s">
+      <c r="N3" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="35" t="s">
+      <c r="O3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="P3" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="36">
+      <c r="Q3" s="35">
         <v>2024</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="R3" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="35" t="s">
+      <c r="S3" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="T3" s="35" t="s">
+      <c r="T3" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="U3" s="35" t="s">
+      <c r="U3" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="V3" s="37">
+      <c r="V3" s="36">
         <v>2025</v>
       </c>
       <c r="W3" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="X3" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="X3" s="21" t="s">
+      <c r="Y3" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="Y3" s="21" t="s">
+      <c r="Z3" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="Z3" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA3" s="37">
+      <c r="AA3" s="36">
         <v>2026</v>
       </c>
       <c r="AB3" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="AE3" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="AF3" s="36">
+        <v>2027</v>
+      </c>
+      <c r="AG3" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="AC3" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD3" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="AE3" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="AF3" s="37">
-        <v>2027</v>
-      </c>
-      <c r="AG3" s="21" t="s">
+      <c r="AH3" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="AH3" s="21" t="s">
+      <c r="AI3" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="AI3" s="21" t="s">
+      <c r="AJ3" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="AJ3" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="AK3" s="37">
+      <c r="AK3" s="36">
         <v>2028</v>
       </c>
     </row>
@@ -12688,7 +13183,7 @@
       <c r="F5" s="18">
         <v>183.99199999999999</v>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="44">
         <f>SUM(C5:F5)</f>
         <v>744.81299999999987</v>
       </c>
@@ -12704,7 +13199,7 @@
       <c r="K5" s="18">
         <v>99.897999999999996</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="44">
         <f>SUM(H5:K5)</f>
         <v>518.28399999999999</v>
       </c>
@@ -12720,7 +13215,7 @@
       <c r="P5" s="18">
         <v>140.227</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="44">
         <f>SUM(M5:P5)</f>
         <v>487.33600000000001</v>
       </c>
@@ -12736,22 +13231,25 @@
       <c r="U5" s="18">
         <v>158.30500000000001</v>
       </c>
-      <c r="V5" s="46">
+      <c r="V5" s="44">
         <f>SUM(R5:U5)</f>
         <v>625.35699999999997</v>
       </c>
       <c r="W5" s="18">
         <v>177.535</v>
       </c>
-      <c r="AA5" s="46">
+      <c r="X5" s="18">
+        <v>199.78800000000001</v>
+      </c>
+      <c r="AA5" s="44">
         <f>SUM(W5:Z5)</f>
-        <v>177.535</v>
-      </c>
-      <c r="AF5" s="46">
+        <v>377.32299999999998</v>
+      </c>
+      <c r="AF5" s="44">
         <f>SUM(AB5:AE5)</f>
         <v>0</v>
       </c>
-      <c r="AK5" s="46">
+      <c r="AK5" s="44">
         <f>SUM(AG5:AJ5)</f>
         <v>0</v>
       </c>
@@ -12764,124 +13262,124 @@
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="38">
+      <c r="G6" s="38"/>
+      <c r="H6" s="37">
         <f t="shared" ref="H6:V6" si="0">(H5-C5)/C5</f>
         <v>-0.20938685748795013</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="37">
         <f t="shared" si="0"/>
         <v>-0.22578642062830848</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="37">
         <f t="shared" si="0"/>
         <v>-0.32309294454569126</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="37">
         <f t="shared" si="0"/>
         <v>-0.45705248054263226</v>
       </c>
-      <c r="L6" s="41">
+      <c r="L6" s="39">
         <f t="shared" si="0"/>
         <v>-0.30414211352379716</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="37">
         <f t="shared" si="0"/>
         <v>-0.50259422065287884</v>
       </c>
-      <c r="N6" s="38">
+      <c r="N6" s="37">
         <f t="shared" si="0"/>
         <v>-0.17844348198053686</v>
       </c>
-      <c r="O6" s="38">
+      <c r="O6" s="37">
         <f t="shared" si="0"/>
         <v>0.19358461538461536</v>
       </c>
-      <c r="P6" s="38">
+      <c r="P6" s="37">
         <f t="shared" si="0"/>
         <v>0.40370177581132766</v>
       </c>
-      <c r="Q6" s="41">
+      <c r="Q6" s="39">
         <f t="shared" si="0"/>
         <v>-5.971243565303961E-2</v>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="37">
         <f t="shared" si="0"/>
         <v>1.1157986236870698</v>
       </c>
-      <c r="S6" s="38">
+      <c r="S6" s="37">
         <f t="shared" si="0"/>
         <v>0.25530841699344281</v>
       </c>
-      <c r="T6" s="38">
+      <c r="T6" s="37">
         <f t="shared" si="0"/>
         <v>7.4391297062500847E-2</v>
       </c>
-      <c r="U6" s="38">
+      <c r="U6" s="37">
         <f t="shared" si="0"/>
         <v>0.1289195376068803</v>
       </c>
-      <c r="V6" s="41">
+      <c r="V6" s="39">
         <f t="shared" si="0"/>
         <v>0.28321527652379458</v>
       </c>
-      <c r="W6" s="38">
+      <c r="W6" s="37">
         <f t="shared" ref="W6" si="1">(W5-R5)/R5</f>
         <v>0.21563512116294509</v>
       </c>
-      <c r="X6" s="38">
+      <c r="X6" s="37">
         <f t="shared" ref="X6" si="2">(X5-S5)/S5</f>
-        <v>-1</v>
-      </c>
-      <c r="Y6" s="38">
+        <v>0.29480233311730392</v>
+      </c>
+      <c r="Y6" s="37">
         <f t="shared" ref="Y6" si="3">(Y5-T5)/T5</f>
         <v>-1</v>
       </c>
-      <c r="Z6" s="38">
+      <c r="Z6" s="37">
         <f t="shared" ref="Z6" si="4">(Z5-U5)/U5</f>
         <v>-1</v>
       </c>
-      <c r="AA6" s="41">
+      <c r="AA6" s="39">
         <f>(AA5-V5)/V5</f>
-        <v>-0.7161061601613159</v>
-      </c>
-      <c r="AB6" s="38">
+        <v>-0.39662784617426528</v>
+      </c>
+      <c r="AB6" s="37">
         <f t="shared" ref="AB6" si="5">(AB5-W5)/W5</f>
         <v>-1</v>
       </c>
-      <c r="AC6" s="38" t="e">
+      <c r="AC6" s="37">
         <f t="shared" ref="AC6" si="6">(AC5-X5)/X5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD6" s="38" t="e">
+        <v>-1</v>
+      </c>
+      <c r="AD6" s="37" t="e">
         <f t="shared" ref="AD6" si="7">(AD5-Y5)/Y5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE6" s="38" t="e">
+      <c r="AE6" s="37" t="e">
         <f t="shared" ref="AE6" si="8">(AE5-Z5)/Z5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF6" s="41">
+      <c r="AF6" s="39">
         <f>(AF5-AA5)/AA5</f>
         <v>-1</v>
       </c>
-      <c r="AG6" s="38" t="e">
+      <c r="AG6" s="37" t="e">
         <f t="shared" ref="AG6" si="9">(AG5-AB5)/AB5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH6" s="38" t="e">
+      <c r="AH6" s="37" t="e">
         <f t="shared" ref="AH6" si="10">(AH5-AC5)/AC5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI6" s="38" t="e">
+      <c r="AI6" s="37" t="e">
         <f t="shared" ref="AI6" si="11">(AI5-AD5)/AD5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ6" s="38" t="e">
+      <c r="AJ6" s="37" t="e">
         <f t="shared" ref="AJ6" si="12">(AJ5-AE5)/AE5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK6" s="41" t="e">
+      <c r="AK6" s="39" t="e">
         <f>(AK5-AF5)/AF5</f>
         <v>#DIV/0!</v>
       </c>
@@ -12918,7 +13416,7 @@
         <f>5+1.8</f>
         <v>6.8</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="44">
         <f>SUM(C8:F8)</f>
         <v>29.766999999999999</v>
       </c>
@@ -12937,7 +13435,7 @@
         <f>6+1.2</f>
         <v>7.2</v>
       </c>
-      <c r="L8" s="46">
+      <c r="L8" s="44">
         <f>SUM(H8:K8)</f>
         <v>21.988</v>
       </c>
@@ -12955,7 +13453,7 @@
       <c r="P8" s="18">
         <v>7.8</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="44">
         <f>SUM(M8:P8)</f>
         <v>18.436</v>
       </c>
@@ -12971,22 +13469,25 @@
       <c r="U8" s="18">
         <v>8.7219999999999995</v>
       </c>
-      <c r="V8" s="46">
+      <c r="V8" s="44">
         <f>SUM(R8:U8)</f>
         <v>33.557000000000002</v>
       </c>
       <c r="W8" s="18">
         <v>12.487</v>
       </c>
-      <c r="AA8" s="46">
+      <c r="X8" s="18">
+        <v>14.625</v>
+      </c>
+      <c r="AA8" s="44">
         <f>SUM(W8:Z8)</f>
-        <v>12.487</v>
-      </c>
-      <c r="AF8" s="46">
+        <v>27.112000000000002</v>
+      </c>
+      <c r="AF8" s="44">
         <f>SUM(AB8:AE8)</f>
         <v>0</v>
       </c>
-      <c r="AK8" s="46">
+      <c r="AK8" s="44">
         <f>SUM(AG8:AJ8)</f>
         <v>0</v>
       </c>
@@ -12999,124 +13500,124 @@
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="38">
+      <c r="G9" s="38"/>
+      <c r="H9" s="37">
         <f t="shared" ref="H9:V9" si="13">(H8-C8)/C8</f>
         <v>-0.23209320799682234</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="37">
         <f t="shared" si="13"/>
         <v>-0.29704918032786876</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9" s="37">
         <f t="shared" si="13"/>
         <v>-0.49538329396607256</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="37">
         <f t="shared" si="13"/>
         <v>5.8823529411764761E-2</v>
       </c>
-      <c r="L9" s="41">
+      <c r="L9" s="39">
         <f t="shared" si="13"/>
         <v>-0.261329660362146</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="37">
         <f t="shared" si="13"/>
         <v>-0.34862068965517251</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="O9" s="38">
+      <c r="O9" s="37">
         <f t="shared" si="13"/>
         <v>-0.45319148936170217</v>
       </c>
-      <c r="P9" s="38">
+      <c r="P9" s="37">
         <f t="shared" si="13"/>
         <v>8.3333333333333287E-2</v>
       </c>
-      <c r="Q9" s="41">
+      <c r="Q9" s="39">
         <f t="shared" si="13"/>
         <v>-0.16154265963252681</v>
       </c>
-      <c r="R9" s="38">
+      <c r="R9" s="37">
         <f t="shared" si="13"/>
         <v>0.99497088406564316</v>
       </c>
-      <c r="S9" s="38">
+      <c r="S9" s="37">
         <f t="shared" si="13"/>
         <v>0.74906716417910435</v>
       </c>
-      <c r="T9" s="38">
+      <c r="T9" s="37">
         <f t="shared" si="13"/>
         <v>2.8124513618677045</v>
       </c>
-      <c r="U9" s="38">
+      <c r="U9" s="37">
         <f t="shared" si="13"/>
         <v>0.11820512820512817</v>
       </c>
-      <c r="V9" s="41">
+      <c r="V9" s="39">
         <f t="shared" si="13"/>
         <v>0.82018876111954886</v>
       </c>
-      <c r="W9" s="38">
+      <c r="W9" s="37">
         <f t="shared" ref="W9" si="14">(W8-R8)/R8</f>
         <v>0.65675998407854586</v>
       </c>
-      <c r="X9" s="38">
+      <c r="X9" s="37">
         <f t="shared" ref="X9" si="15">(X8-S8)/S8</f>
-        <v>-1</v>
-      </c>
-      <c r="Y9" s="38">
+        <v>0.95</v>
+      </c>
+      <c r="Y9" s="37">
         <f t="shared" ref="Y9" si="16">(Y8-T8)/T8</f>
         <v>-1</v>
       </c>
-      <c r="Z9" s="38">
+      <c r="Z9" s="37">
         <f t="shared" ref="Z9" si="17">(Z8-U8)/U8</f>
         <v>-1</v>
       </c>
-      <c r="AA9" s="41">
+      <c r="AA9" s="39">
         <f t="shared" ref="AA9" si="18">(AA8-V8)/V8</f>
-        <v>-0.62788687904163065</v>
-      </c>
-      <c r="AB9" s="38">
+        <v>-0.19206126888577643</v>
+      </c>
+      <c r="AB9" s="37">
         <f t="shared" ref="AB9" si="19">(AB8-W8)/W8</f>
         <v>-1</v>
       </c>
-      <c r="AC9" s="38" t="e">
+      <c r="AC9" s="37">
         <f t="shared" ref="AC9" si="20">(AC8-X8)/X8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD9" s="38" t="e">
+        <v>-1</v>
+      </c>
+      <c r="AD9" s="37" t="e">
         <f t="shared" ref="AD9" si="21">(AD8-Y8)/Y8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE9" s="38" t="e">
+      <c r="AE9" s="37" t="e">
         <f t="shared" ref="AE9" si="22">(AE8-Z8)/Z8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF9" s="41">
+      <c r="AF9" s="39">
         <f t="shared" ref="AF9" si="23">(AF8-AA8)/AA8</f>
         <v>-1</v>
       </c>
-      <c r="AG9" s="38" t="e">
+      <c r="AG9" s="37" t="e">
         <f t="shared" ref="AG9" si="24">(AG8-AB8)/AB8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH9" s="38" t="e">
+      <c r="AH9" s="37" t="e">
         <f t="shared" ref="AH9" si="25">(AH8-AC8)/AC8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI9" s="38" t="e">
+      <c r="AI9" s="37" t="e">
         <f t="shared" ref="AI9" si="26">(AI8-AD8)/AD8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ9" s="38" t="e">
+      <c r="AJ9" s="37" t="e">
         <f t="shared" ref="AJ9" si="27">(AJ8-AE8)/AE8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK9" s="41" t="e">
+      <c r="AK9" s="39" t="e">
         <f t="shared" ref="AK9" si="28">(AK8-AF8)/AF8</f>
         <v>#DIV/0!</v>
       </c>
@@ -13149,7 +13650,7 @@
       <c r="F11" s="18">
         <v>0.48199999999999998</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="44">
         <f>SUM(C11:F11)</f>
         <v>1.9509999999999998</v>
       </c>
@@ -13165,7 +13666,7 @@
       <c r="K11" s="18">
         <v>0.98399999999999999</v>
       </c>
-      <c r="L11" s="46">
+      <c r="L11" s="44">
         <f>SUM(H11:K11)</f>
         <v>2.3010000000000002</v>
       </c>
@@ -13181,7 +13682,7 @@
       <c r="P11" s="18">
         <v>2</v>
       </c>
-      <c r="Q11" s="46">
+      <c r="Q11" s="44">
         <f>SUM(M11:P11)</f>
         <v>5.4380000000000006</v>
       </c>
@@ -13197,22 +13698,25 @@
       <c r="U11" s="18">
         <v>2.4809999999999999</v>
       </c>
-      <c r="V11" s="46">
+      <c r="V11" s="44">
         <f>SUM(R11:U11)</f>
         <v>8.6180000000000003</v>
       </c>
       <c r="W11" s="18">
         <v>2.4209999999999998</v>
       </c>
-      <c r="AA11" s="46">
+      <c r="X11" s="18">
+        <v>4</v>
+      </c>
+      <c r="AA11" s="44">
         <f>SUM(W11:Z11)</f>
-        <v>2.4209999999999998</v>
-      </c>
-      <c r="AF11" s="46">
+        <v>6.4209999999999994</v>
+      </c>
+      <c r="AF11" s="44">
         <f>SUM(AB11:AE11)</f>
         <v>0</v>
       </c>
-      <c r="AK11" s="46">
+      <c r="AK11" s="44">
         <f>SUM(AG11:AJ11)</f>
         <v>0</v>
       </c>
@@ -13225,121 +13729,121 @@
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38">
+      <c r="G12" s="38"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37">
         <f t="shared" ref="I12:V12" si="29">(I11-D11)/D11</f>
         <v>-0.61784287616511324</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12" s="37">
         <f t="shared" si="29"/>
         <v>-0.66155988857938719</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12" s="37">
         <f t="shared" si="29"/>
         <v>1.04149377593361</v>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="39">
         <f t="shared" si="29"/>
         <v>0.17939518195797044</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12" s="37">
         <f t="shared" si="29"/>
         <v>1.1537484116899619</v>
       </c>
-      <c r="N12" s="38">
+      <c r="N12" s="37">
         <f t="shared" si="29"/>
         <v>1.5888501742160281</v>
       </c>
-      <c r="O12" s="38">
+      <c r="O12" s="37">
         <f t="shared" si="29"/>
         <v>3.1152263374485596</v>
       </c>
-      <c r="P12" s="38">
+      <c r="P12" s="37">
         <f t="shared" si="29"/>
         <v>1.032520325203252</v>
       </c>
-      <c r="Q12" s="41">
+      <c r="Q12" s="39">
         <f t="shared" si="29"/>
         <v>1.3633202955236854</v>
       </c>
-      <c r="R12" s="38">
+      <c r="R12" s="37">
         <f t="shared" si="29"/>
         <v>-0.12271386430678463</v>
       </c>
-      <c r="S12" s="38">
+      <c r="S12" s="37">
         <f t="shared" si="29"/>
         <v>1.960969044414536</v>
       </c>
-      <c r="T12" s="38">
+      <c r="T12" s="37">
         <f t="shared" si="29"/>
         <v>1.4500000000000002</v>
       </c>
-      <c r="U12" s="38">
+      <c r="U12" s="37">
         <f t="shared" si="29"/>
         <v>0.24049999999999994</v>
       </c>
-      <c r="V12" s="41">
+      <c r="V12" s="39">
         <f t="shared" si="29"/>
         <v>0.58477381390216976</v>
       </c>
-      <c r="W12" s="38">
+      <c r="W12" s="37">
         <f t="shared" ref="W12" si="30">(W11-R11)/R11</f>
         <v>0.62811028917283096</v>
       </c>
-      <c r="X12" s="38">
+      <c r="X12" s="37">
         <f t="shared" ref="X12" si="31">(X11-S11)/S11</f>
-        <v>-1</v>
-      </c>
-      <c r="Y12" s="38">
+        <v>0.81818181818181801</v>
+      </c>
+      <c r="Y12" s="37">
         <f>(Y11-T11)/T11</f>
         <v>-1</v>
       </c>
-      <c r="Z12" s="38">
+      <c r="Z12" s="37">
         <f t="shared" ref="Z12" si="32">(Z11-U11)/U11</f>
         <v>-1</v>
       </c>
-      <c r="AA12" s="41">
+      <c r="AA12" s="39">
         <f t="shared" ref="AA12" si="33">(AA11-V11)/V11</f>
-        <v>-0.71907635182176843</v>
-      </c>
-      <c r="AB12" s="38">
+        <v>-0.2549315386400558</v>
+      </c>
+      <c r="AB12" s="37">
         <f t="shared" ref="AB12" si="34">(AB11-W11)/W11</f>
         <v>-1</v>
       </c>
-      <c r="AC12" s="38" t="e">
+      <c r="AC12" s="37">
         <f t="shared" ref="AC12" si="35">(AC11-X11)/X11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD12" s="38" t="e">
+        <v>-1</v>
+      </c>
+      <c r="AD12" s="37" t="e">
         <f>(AD11-Y11)/Y11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE12" s="38" t="e">
+      <c r="AE12" s="37" t="e">
         <f t="shared" ref="AE12" si="36">(AE11-Z11)/Z11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF12" s="41">
+      <c r="AF12" s="39">
         <f t="shared" ref="AF12" si="37">(AF11-AA11)/AA11</f>
         <v>-1</v>
       </c>
-      <c r="AG12" s="38" t="e">
+      <c r="AG12" s="37" t="e">
         <f t="shared" ref="AG12" si="38">(AG11-AB11)/AB11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH12" s="38" t="e">
+      <c r="AH12" s="37" t="e">
         <f t="shared" ref="AH12" si="39">(AH11-AC11)/AC11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI12" s="38" t="e">
+      <c r="AI12" s="37" t="e">
         <f>(AI11-AD11)/AD11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ12" s="38" t="e">
+      <c r="AJ12" s="37" t="e">
         <f t="shared" ref="AJ12" si="40">(AJ11-AE11)/AE11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK12" s="41" t="e">
+      <c r="AK12" s="39" t="e">
         <f t="shared" ref="AK12" si="41">(AK11-AF11)/AF11</f>
         <v>#DIV/0!</v>
       </c>
@@ -13353,109 +13857,109 @@
       <c r="B16" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="35">
         <v>2022</v>
       </c>
-      <c r="H16" s="35" t="s">
+      <c r="H16" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="I16" s="35" t="s">
+      <c r="I16" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="J16" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="K16" s="35" t="s">
+      <c r="K16" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="35">
         <v>2023</v>
       </c>
-      <c r="M16" s="35" t="s">
+      <c r="M16" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="N16" s="35" t="s">
+      <c r="N16" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="35" t="s">
+      <c r="O16" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="P16" s="35" t="s">
+      <c r="P16" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="Q16" s="36">
+      <c r="Q16" s="35">
         <v>2024</v>
       </c>
-      <c r="R16" s="35" t="s">
+      <c r="R16" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="S16" s="35" t="s">
+      <c r="S16" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="T16" s="35" t="s">
+      <c r="T16" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="U16" s="35" t="s">
+      <c r="U16" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="36">
         <v>2025</v>
       </c>
-      <c r="W16" s="35" t="s">
+      <c r="W16" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="X16" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="X16" s="35" t="s">
+      <c r="Y16" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="Y16" s="35" t="s">
+      <c r="Z16" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="Z16" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="36">
         <v>2026</v>
       </c>
-      <c r="AB16" s="74" t="s">
+      <c r="AB16" s="72" t="s">
+        <v>251</v>
+      </c>
+      <c r="AC16" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD16" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="AE16" s="73" t="s">
+        <v>248</v>
+      </c>
+      <c r="AF16" s="36">
+        <v>2027</v>
+      </c>
+      <c r="AG16" s="72" t="s">
         <v>252</v>
       </c>
-      <c r="AC16" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD16" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="AE16" s="75" t="s">
-        <v>249</v>
-      </c>
-      <c r="AF16" s="37">
-        <v>2027</v>
-      </c>
-      <c r="AG16" s="74" t="s">
+      <c r="AH16" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="AH16" s="35" t="s">
+      <c r="AI16" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="AI16" s="35" t="s">
+      <c r="AJ16" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="AJ16" s="75" t="s">
-        <v>256</v>
-      </c>
-      <c r="AK16" s="37">
+      <c r="AK16" s="36">
         <v>2028</v>
       </c>
     </row>
@@ -13471,88 +13975,89 @@
       <c r="AF17" s="31"/>
       <c r="AK17" s="31"/>
     </row>
-    <row r="18" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
+    <row r="18" spans="2:37" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="18">
         <v>122.246</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="18">
         <v>126.404</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="18">
         <v>126.242</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="18">
         <v>108.90600000000001</v>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="44">
         <f>SUM(C18:F18)</f>
         <v>483.798</v>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="18">
         <v>69.75</v>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="18">
         <v>84.358000000000004</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="18">
         <v>80</v>
       </c>
-      <c r="K18" s="34">
+      <c r="K18" s="18">
         <v>67.411000000000001</v>
       </c>
-      <c r="L18" s="39">
+      <c r="L18" s="44">
         <f>SUM(H18:K18)</f>
         <v>301.51900000000001</v>
       </c>
-      <c r="M18" s="34">
+      <c r="M18" s="18">
         <v>54.198</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="18">
         <v>83</v>
       </c>
-      <c r="O18" s="34">
+      <c r="O18" s="18">
         <v>108.96</v>
       </c>
-      <c r="P18" s="34">
+      <c r="P18" s="18">
         <v>94.311999999999998</v>
       </c>
-      <c r="Q18" s="39">
+      <c r="Q18" s="44">
         <f>SUM(M18:P18)</f>
         <v>340.47</v>
       </c>
-      <c r="R18" s="34">
+      <c r="R18" s="18">
         <v>88.475999999999999</v>
       </c>
-      <c r="S18" s="1">
+      <c r="S18" s="18">
         <v>100</v>
       </c>
-      <c r="T18" s="1">
+      <c r="T18" s="18">
         <v>112</v>
       </c>
-      <c r="U18" s="1">
+      <c r="U18" s="18">
         <v>100</v>
       </c>
-      <c r="V18" s="39">
+      <c r="V18" s="44">
         <f>SUM(R18:U18)</f>
         <v>400.476</v>
       </c>
-      <c r="W18" s="34">
+      <c r="W18" s="18">
         <v>115.142</v>
       </c>
-      <c r="AA18" s="39">
+      <c r="X18" s="18">
+        <v>125.227</v>
+      </c>
+      <c r="AA18" s="44">
         <f>SUM(W18:Z18)</f>
-        <v>115.142</v>
-      </c>
-      <c r="AB18" s="34"/>
-      <c r="AF18" s="39">
+        <v>240.369</v>
+      </c>
+      <c r="AF18" s="44">
         <f>SUM(AB18:AE18)</f>
         <v>0</v>
       </c>
-      <c r="AG18" s="34"/>
-      <c r="AK18" s="39">
+      <c r="AK18" s="44">
         <f>SUM(AG18:AJ18)</f>
         <v>0</v>
       </c>
@@ -13566,123 +14071,123 @@
       <c r="E19" s="30"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32"/>
-      <c r="H19" s="38">
+      <c r="H19" s="37">
         <f t="shared" ref="H19:V19" si="42">(H18-C18)/C18</f>
         <v>-0.42942918377697425</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19" s="37">
         <f t="shared" si="42"/>
         <v>-0.33263187873801459</v>
       </c>
-      <c r="J19" s="38">
+      <c r="J19" s="37">
         <f t="shared" si="42"/>
         <v>-0.36629647819267758</v>
       </c>
-      <c r="K19" s="38">
+      <c r="K19" s="37">
         <f t="shared" si="42"/>
         <v>-0.38101665656621309</v>
       </c>
-      <c r="L19" s="41">
+      <c r="L19" s="39">
         <f t="shared" si="42"/>
         <v>-0.37676674975919699</v>
       </c>
-      <c r="M19" s="38">
+      <c r="M19" s="37">
         <f t="shared" si="42"/>
         <v>-0.22296774193548385</v>
       </c>
-      <c r="N19" s="38">
+      <c r="N19" s="37">
         <f t="shared" si="42"/>
         <v>-1.6098058275445176E-2</v>
       </c>
-      <c r="O19" s="38">
+      <c r="O19" s="37">
         <f t="shared" si="42"/>
         <v>0.36199999999999993</v>
       </c>
-      <c r="P19" s="38">
+      <c r="P19" s="37">
         <f t="shared" si="42"/>
         <v>0.39905950067496399</v>
       </c>
-      <c r="Q19" s="41">
+      <c r="Q19" s="39">
         <f t="shared" si="42"/>
         <v>0.12918257224254531</v>
       </c>
-      <c r="R19" s="38">
+      <c r="R19" s="37">
         <f t="shared" si="42"/>
         <v>0.63245876231595255</v>
       </c>
-      <c r="S19" s="38">
+      <c r="S19" s="37">
         <f>(S18-N18)/N18</f>
         <v>0.20481927710843373</v>
       </c>
-      <c r="T19" s="38">
+      <c r="T19" s="37">
         <f t="shared" si="42"/>
         <v>2.7900146842878181E-2</v>
       </c>
-      <c r="U19" s="38">
+      <c r="U19" s="37">
         <f t="shared" si="42"/>
         <v>6.0310458902366637E-2</v>
       </c>
-      <c r="V19" s="41">
+      <c r="V19" s="39">
         <f t="shared" si="42"/>
         <v>0.17624460304872666</v>
       </c>
-      <c r="W19" s="38">
+      <c r="W19" s="37">
         <f t="shared" ref="W19" si="43">(W18-R18)/R18</f>
         <v>0.30139246801392466</v>
       </c>
-      <c r="X19" s="38">
+      <c r="X19" s="37">
         <f>(X18-S18)/S18</f>
-        <v>-1</v>
-      </c>
-      <c r="Y19" s="38">
+        <v>0.25227000000000005</v>
+      </c>
+      <c r="Y19" s="37">
         <f t="shared" ref="Y19" si="44">(Y18-T18)/T18</f>
         <v>-1</v>
       </c>
-      <c r="Z19" s="38">
+      <c r="Z19" s="37">
         <f t="shared" ref="Z19" si="45">(Z18-U18)/U18</f>
         <v>-1</v>
       </c>
-      <c r="AA19" s="41">
+      <c r="AA19" s="39">
         <f t="shared" ref="AA19" si="46">(AA18-V18)/V18</f>
-        <v>-0.71248714030303939</v>
-      </c>
-      <c r="AB19" s="38">
+        <v>-0.39979174782009408</v>
+      </c>
+      <c r="AB19" s="37">
         <f t="shared" ref="AB19" si="47">(AB18-W18)/W18</f>
         <v>-1</v>
       </c>
-      <c r="AC19" s="38" t="e">
+      <c r="AC19" s="37">
         <f>(AC18-X18)/X18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD19" s="38" t="e">
+        <v>-1</v>
+      </c>
+      <c r="AD19" s="37" t="e">
         <f t="shared" ref="AD19" si="48">(AD18-Y18)/Y18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE19" s="38" t="e">
+      <c r="AE19" s="37" t="e">
         <f t="shared" ref="AE19" si="49">(AE18-Z18)/Z18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF19" s="41">
+      <c r="AF19" s="39">
         <f t="shared" ref="AF19" si="50">(AF18-AA18)/AA18</f>
         <v>-1</v>
       </c>
-      <c r="AG19" s="38" t="e">
+      <c r="AG19" s="37" t="e">
         <f t="shared" ref="AG19" si="51">(AG18-AB18)/AB18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH19" s="38" t="e">
+      <c r="AH19" s="37" t="e">
         <f>(AH18-AC18)/AC18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI19" s="38" t="e">
+      <c r="AI19" s="37" t="e">
         <f t="shared" ref="AI19" si="52">(AI18-AD18)/AD18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ19" s="38" t="e">
+      <c r="AJ19" s="37" t="e">
         <f t="shared" ref="AJ19" si="53">(AJ18-AE18)/AE18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK19" s="41" t="e">
+      <c r="AK19" s="39" t="e">
         <f t="shared" ref="AK19" si="54">(AK18-AF18)/AF18</f>
         <v>#DIV/0!</v>
       </c>
@@ -13699,97 +14204,98 @@
       <c r="AF20" s="31"/>
       <c r="AK20" s="31"/>
     </row>
-    <row r="21" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+    <row r="21" spans="2:37" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="18">
         <f>39.783+14.192</f>
         <v>53.975000000000001</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="18">
         <f>48.205+16.755</f>
         <v>64.959999999999994</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="18">
         <f>51.815+14.374</f>
         <v>66.188999999999993</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="18">
         <f>51.739+22.3</f>
         <v>74.039000000000001</v>
       </c>
-      <c r="G21" s="39">
+      <c r="G21" s="44">
         <f>SUM(C21:F21)</f>
         <v>259.16300000000001</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="18">
         <f>45.362+23.56</f>
         <v>68.921999999999997</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="18">
         <f>29.873+34.522</f>
         <v>64.394999999999996</v>
       </c>
-      <c r="J21" s="34">
+      <c r="J21" s="18">
         <f>23.709+26.491</f>
         <v>50.2</v>
       </c>
-      <c r="K21" s="34">
+      <c r="K21" s="18">
         <f>18.26+18.752</f>
         <v>37.012</v>
       </c>
-      <c r="L21" s="39">
+      <c r="L21" s="44">
         <f>SUM(H21:K21)</f>
         <v>220.529</v>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="18">
         <v>17.273</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="18">
         <f>26.565+14.899</f>
         <v>41.463999999999999</v>
       </c>
-      <c r="O21" s="34">
+      <c r="O21" s="18">
         <v>44</v>
       </c>
-      <c r="P21" s="34">
+      <c r="P21" s="18">
         <v>48</v>
       </c>
-      <c r="Q21" s="39">
+      <c r="Q21" s="44">
         <f>SUM(M21:P21)</f>
         <v>150.73699999999999</v>
       </c>
-      <c r="R21" s="34">
+      <c r="R21" s="18">
         <v>60.362000000000002</v>
       </c>
-      <c r="S21" s="1">
+      <c r="S21" s="18">
         <v>59</v>
       </c>
-      <c r="T21" s="1">
+      <c r="T21" s="18">
         <v>62</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21" s="18">
         <v>63</v>
       </c>
-      <c r="V21" s="39">
+      <c r="V21" s="44">
         <f>SUM(R21:U21)</f>
         <v>244.36199999999999</v>
       </c>
-      <c r="W21" s="34">
+      <c r="W21" s="18">
         <v>72.17</v>
       </c>
-      <c r="AA21" s="39">
+      <c r="X21" s="18">
+        <v>86.052000000000007</v>
+      </c>
+      <c r="AA21" s="44">
         <f>SUM(W21:Z21)</f>
-        <v>72.17</v>
-      </c>
-      <c r="AB21" s="34"/>
-      <c r="AF21" s="39">
+        <v>158.22200000000001</v>
+      </c>
+      <c r="AF21" s="44">
         <f>SUM(AB21:AE21)</f>
         <v>0</v>
       </c>
-      <c r="AG21" s="34"/>
-      <c r="AK21" s="39">
+      <c r="AK21" s="44">
         <f>SUM(AG21:AJ21)</f>
         <v>0</v>
       </c>
@@ -13803,123 +14309,123 @@
       <c r="E22" s="30"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32"/>
-      <c r="H22" s="38">
+      <c r="H22" s="37">
         <f t="shared" ref="H22:V22" si="55">(H21-C21)/C21</f>
         <v>0.2769245020842982</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="37">
         <f t="shared" si="55"/>
         <v>-8.6976600985221326E-3</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="37">
         <f t="shared" si="55"/>
         <v>-0.241565819093807</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22" s="37">
         <f t="shared" si="55"/>
         <v>-0.50010129796458624</v>
       </c>
-      <c r="L22" s="41">
+      <c r="L22" s="39">
         <f t="shared" si="55"/>
         <v>-0.149072205523165</v>
       </c>
-      <c r="M22" s="38">
+      <c r="M22" s="37">
         <f t="shared" si="55"/>
         <v>-0.74938336090072843</v>
       </c>
-      <c r="N22" s="38">
+      <c r="N22" s="37">
         <f t="shared" si="55"/>
         <v>-0.35609907601521856</v>
       </c>
-      <c r="O22" s="38">
+      <c r="O22" s="37">
         <f t="shared" si="55"/>
         <v>-0.12350597609561757</v>
       </c>
-      <c r="P22" s="38">
+      <c r="P22" s="37">
         <f t="shared" si="55"/>
         <v>0.29687668864152167</v>
       </c>
-      <c r="Q22" s="41">
+      <c r="Q22" s="39">
         <f t="shared" si="55"/>
         <v>-0.31647538418983445</v>
       </c>
-      <c r="R22" s="38">
+      <c r="R22" s="37">
         <f t="shared" si="55"/>
         <v>2.4945869275748276</v>
       </c>
-      <c r="S22" s="38">
+      <c r="S22" s="37">
         <f t="shared" si="55"/>
         <v>0.42292108817287288</v>
       </c>
-      <c r="T22" s="38">
+      <c r="T22" s="37">
         <f t="shared" si="55"/>
         <v>0.40909090909090912</v>
       </c>
-      <c r="U22" s="38">
+      <c r="U22" s="37">
         <f t="shared" si="55"/>
         <v>0.3125</v>
       </c>
-      <c r="V22" s="41">
+      <c r="V22" s="39">
         <f t="shared" si="55"/>
         <v>0.62111492201649232</v>
       </c>
-      <c r="W22" s="38">
+      <c r="W22" s="37">
         <f t="shared" ref="W22" si="56">(W21-R21)/R21</f>
         <v>0.19561976077664756</v>
       </c>
-      <c r="X22" s="38">
+      <c r="X22" s="37">
         <f t="shared" ref="X22" si="57">(X21-S21)/S21</f>
-        <v>-1</v>
-      </c>
-      <c r="Y22" s="38">
+        <v>0.45850847457627131</v>
+      </c>
+      <c r="Y22" s="37">
         <f t="shared" ref="Y22" si="58">(Y21-T21)/T21</f>
         <v>-1</v>
       </c>
-      <c r="Z22" s="38">
+      <c r="Z22" s="37">
         <f t="shared" ref="Z22" si="59">(Z21-U21)/U21</f>
         <v>-1</v>
       </c>
-      <c r="AA22" s="41">
+      <c r="AA22" s="39">
         <f t="shared" ref="AA22" si="60">(AA21-V21)/V21</f>
-        <v>-0.70465948060664096</v>
-      </c>
-      <c r="AB22" s="38">
+        <v>-0.35250980103289375</v>
+      </c>
+      <c r="AB22" s="37">
         <f t="shared" ref="AB22" si="61">(AB21-W21)/W21</f>
         <v>-1</v>
       </c>
-      <c r="AC22" s="38" t="e">
+      <c r="AC22" s="37">
         <f t="shared" ref="AC22" si="62">(AC21-X21)/X21</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD22" s="38" t="e">
+        <v>-1</v>
+      </c>
+      <c r="AD22" s="37" t="e">
         <f t="shared" ref="AD22" si="63">(AD21-Y21)/Y21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE22" s="38" t="e">
+      <c r="AE22" s="37" t="e">
         <f t="shared" ref="AE22" si="64">(AE21-Z21)/Z21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF22" s="41">
+      <c r="AF22" s="39">
         <f t="shared" ref="AF22" si="65">(AF21-AA21)/AA21</f>
         <v>-1</v>
       </c>
-      <c r="AG22" s="38" t="e">
+      <c r="AG22" s="37" t="e">
         <f t="shared" ref="AG22" si="66">(AG21-AB21)/AB21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH22" s="38" t="e">
+      <c r="AH22" s="37" t="e">
         <f t="shared" ref="AH22" si="67">(AH21-AC21)/AC21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI22" s="38" t="e">
+      <c r="AI22" s="37" t="e">
         <f t="shared" ref="AI22" si="68">(AI21-AD21)/AD21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ22" s="38" t="e">
+      <c r="AJ22" s="37" t="e">
         <f t="shared" ref="AJ22" si="69">(AJ21-AE21)/AE21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK22" s="41" t="e">
+      <c r="AK22" s="39" t="e">
         <f t="shared" ref="AK22" si="70">(AK21-AF21)/AF21</f>
         <v>#DIV/0!</v>
       </c>
@@ -13936,88 +14442,89 @@
       <c r="AF23" s="31"/>
       <c r="AK23" s="31"/>
     </row>
-    <row r="24" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
+    <row r="24" spans="2:37" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="18">
         <v>5.8</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="18">
         <v>7.7</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="18">
         <v>8.9</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="18">
         <v>6.5</v>
       </c>
-      <c r="G24" s="39">
+      <c r="G24" s="44">
         <f>SUM(C24:F24)</f>
         <v>28.9</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="18">
         <v>5.6</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="18">
         <v>3.7</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="18">
         <v>3.3</v>
       </c>
-      <c r="K24" s="34">
+      <c r="K24" s="18">
         <v>2.4</v>
       </c>
-      <c r="L24" s="39">
+      <c r="L24" s="44">
         <f>SUM(H24:K24)</f>
         <v>15.000000000000002</v>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="18">
         <v>2</v>
       </c>
-      <c r="N24" s="34">
+      <c r="N24" s="18">
         <v>2.891</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O24" s="18">
         <v>3</v>
       </c>
-      <c r="P24" s="34">
+      <c r="P24" s="18">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Q24" s="39">
+      <c r="Q24" s="44">
         <f>SUM(M24:P24)</f>
         <v>12.291</v>
       </c>
-      <c r="R24" s="34">
+      <c r="R24" s="18">
         <v>5.6509999999999998</v>
       </c>
-      <c r="S24" s="1">
+      <c r="S24" s="18">
         <v>4</v>
       </c>
-      <c r="T24" s="1">
+      <c r="T24" s="18">
         <v>5</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="18">
         <v>6</v>
       </c>
-      <c r="V24" s="39">
+      <c r="V24" s="44">
         <f>SUM(R24:U24)</f>
         <v>20.651</v>
       </c>
-      <c r="W24" s="34">
+      <c r="W24" s="18">
         <v>4.9779999999999998</v>
       </c>
-      <c r="AA24" s="39">
+      <c r="X24" s="18">
+        <v>7.22</v>
+      </c>
+      <c r="AA24" s="44">
         <f>SUM(W24:Z24)</f>
-        <v>4.9779999999999998</v>
-      </c>
-      <c r="AB24" s="34"/>
-      <c r="AF24" s="39">
+        <v>12.198</v>
+      </c>
+      <c r="AF24" s="44">
         <f>SUM(AB24:AE24)</f>
         <v>0</v>
       </c>
-      <c r="AG24" s="34"/>
-      <c r="AK24" s="39">
+      <c r="AK24" s="44">
         <f>SUM(AG24:AJ24)</f>
         <v>0</v>
       </c>
@@ -14031,123 +14538,123 @@
       <c r="E25" s="30"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32"/>
-      <c r="H25" s="38">
+      <c r="H25" s="37">
         <f t="shared" ref="H25:V25" si="71">(H24-C24)/C24</f>
         <v>-3.4482758620689689E-2</v>
       </c>
-      <c r="I25" s="38">
+      <c r="I25" s="37">
         <f t="shared" si="71"/>
         <v>-0.51948051948051943</v>
       </c>
-      <c r="J25" s="38">
+      <c r="J25" s="37">
         <f t="shared" si="71"/>
         <v>-0.6292134831460674</v>
       </c>
-      <c r="K25" s="38">
+      <c r="K25" s="37">
         <f t="shared" si="71"/>
         <v>-0.63076923076923075</v>
       </c>
-      <c r="L25" s="41">
+      <c r="L25" s="39">
         <f t="shared" si="71"/>
         <v>-0.48096885813148782</v>
       </c>
-      <c r="M25" s="38">
+      <c r="M25" s="37">
         <f t="shared" si="71"/>
         <v>-0.64285714285714279</v>
       </c>
-      <c r="N25" s="38">
+      <c r="N25" s="37">
         <f t="shared" si="71"/>
         <v>-0.21864864864864869</v>
       </c>
-      <c r="O25" s="38">
+      <c r="O25" s="37">
         <f t="shared" si="71"/>
         <v>-9.0909090909090856E-2</v>
       </c>
-      <c r="P25" s="38">
+      <c r="P25" s="37">
         <f t="shared" si="71"/>
         <v>0.83333333333333359</v>
       </c>
-      <c r="Q25" s="41">
+      <c r="Q25" s="39">
         <f t="shared" si="71"/>
         <v>-0.18060000000000007</v>
       </c>
-      <c r="R25" s="38">
+      <c r="R25" s="37">
         <f t="shared" si="71"/>
         <v>1.8254999999999999</v>
       </c>
-      <c r="S25" s="38">
+      <c r="S25" s="37">
         <f t="shared" si="71"/>
         <v>0.38360428917329642</v>
       </c>
-      <c r="T25" s="38">
+      <c r="T25" s="37">
         <f t="shared" si="71"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="U25" s="38">
+      <c r="U25" s="37">
         <f t="shared" si="71"/>
         <v>0.36363636363636354</v>
       </c>
-      <c r="V25" s="41">
+      <c r="V25" s="39">
         <f t="shared" si="71"/>
         <v>0.68017248393133178</v>
       </c>
-      <c r="W25" s="38">
+      <c r="W25" s="37">
         <f t="shared" ref="W25" si="72">(W24-R24)/R24</f>
         <v>-0.11909396566979297</v>
       </c>
-      <c r="X25" s="38">
+      <c r="X25" s="37">
         <f t="shared" ref="X25" si="73">(X24-S24)/S24</f>
-        <v>-1</v>
-      </c>
-      <c r="Y25" s="38">
+        <v>0.80499999999999994</v>
+      </c>
+      <c r="Y25" s="37">
         <f t="shared" ref="Y25" si="74">(Y24-T24)/T24</f>
         <v>-1</v>
       </c>
-      <c r="Z25" s="38">
+      <c r="Z25" s="37">
         <f t="shared" ref="Z25" si="75">(Z24-U24)/U24</f>
         <v>-1</v>
       </c>
-      <c r="AA25" s="41">
+      <c r="AA25" s="39">
         <f t="shared" ref="AA25" si="76">(AA24-V24)/V24</f>
-        <v>-0.75894629800009683</v>
-      </c>
-      <c r="AB25" s="38">
+        <v>-0.40932642487046628</v>
+      </c>
+      <c r="AB25" s="37">
         <f t="shared" ref="AB25" si="77">(AB24-W24)/W24</f>
         <v>-1</v>
       </c>
-      <c r="AC25" s="38" t="e">
+      <c r="AC25" s="37">
         <f t="shared" ref="AC25" si="78">(AC24-X24)/X24</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD25" s="38" t="e">
+        <v>-1</v>
+      </c>
+      <c r="AD25" s="37" t="e">
         <f t="shared" ref="AD25" si="79">(AD24-Y24)/Y24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE25" s="38" t="e">
+      <c r="AE25" s="37" t="e">
         <f t="shared" ref="AE25" si="80">(AE24-Z24)/Z24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF25" s="41">
+      <c r="AF25" s="39">
         <f t="shared" ref="AF25" si="81">(AF24-AA24)/AA24</f>
         <v>-1</v>
       </c>
-      <c r="AG25" s="38" t="e">
+      <c r="AG25" s="37" t="e">
         <f t="shared" ref="AG25" si="82">(AG24-AB24)/AB24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH25" s="38" t="e">
+      <c r="AH25" s="37" t="e">
         <f t="shared" ref="AH25" si="83">(AH24-AC24)/AC24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI25" s="38" t="e">
+      <c r="AI25" s="37" t="e">
         <f t="shared" ref="AI25" si="84">(AI24-AD24)/AD24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ25" s="38" t="e">
+      <c r="AJ25" s="37" t="e">
         <f t="shared" ref="AJ25" si="85">(AJ24-AE24)/AE24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK25" s="41" t="e">
+      <c r="AK25" s="39" t="e">
         <f t="shared" ref="AK25" si="86">(AK24-AF24)/AF24</f>
         <v>#DIV/0!</v>
       </c>
@@ -14159,7 +14666,7 @@
       <c r="P26" s="14"/>
     </row>
     <row r="32" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="S32" s="73"/>
+      <c r="S32" s="71"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14192,70 +14699,70 @@
     </row>
     <row r="6" spans="3:6" ht="92" x14ac:dyDescent="1">
       <c r="C6" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="D6" s="48">
+        <v>185</v>
+      </c>
+      <c r="D6" s="46">
         <f>Modell!$B$9/(Modell!AG4*Modell!$B$11)</f>
-        <v>2.5850568251252604</v>
-      </c>
-      <c r="E6" s="48">
+        <v>3.1140804106073565</v>
+      </c>
+      <c r="E6" s="46">
         <f>Modell!$B$9/(Modell!AH4*Modell!$B$11)</f>
-        <v>2.154214020937717</v>
-      </c>
-      <c r="F6" s="48">
+        <v>2.5950670088394645</v>
+      </c>
+      <c r="F6" s="46">
         <f>Modell!$B$9/(Modell!AI4*Modell!$B$11)</f>
-        <v>1.7951783507814307</v>
+        <v>2.1625558406995533</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="92" x14ac:dyDescent="1">
       <c r="C7" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="46">
         <f>Modell!$B$9/(Modell!$B$11*Modell!AF9)</f>
-        <v>24.496188185885288</v>
-      </c>
-      <c r="E7" s="48">
+        <v>29.509254505660781</v>
+      </c>
+      <c r="E7" s="46">
         <f>Modell!$B$9/(Modell!$B$11*Modell!AG9)</f>
-        <v>17.132354287049012</v>
-      </c>
-      <c r="F7" s="48">
+        <v>20.638435625220392</v>
+      </c>
+      <c r="F7" s="46">
         <f>Modell!$B$9/(Modell!$B$11*Modell!AH9)</f>
-        <v>12.456486853534486</v>
+        <v>15.005666923279415</v>
       </c>
     </row>
     <row r="8" spans="3:6" ht="92" x14ac:dyDescent="1">
       <c r="C8" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="46">
         <f>Modell!$B$9/(Modell!$B$11*Modell!AF11)</f>
-        <v>39.401079080856555</v>
-      </c>
-      <c r="E8" s="48">
+        <v>47.464383502107857</v>
+      </c>
+      <c r="E8" s="46">
         <f>Modell!$B$9/(Modell!$B$11*Modell!AG11)</f>
-        <v>23.295670251926538</v>
-      </c>
-      <c r="F8" s="48">
+        <v>28.063054428204996</v>
+      </c>
+      <c r="F8" s="46">
         <f>Modell!$B$9/(Modell!$B$11*Modell!AH11)</f>
-        <v>15.423341115953228</v>
+        <v>18.579678391780675</v>
       </c>
     </row>
     <row r="9" spans="3:6" ht="92" x14ac:dyDescent="1">
       <c r="C9" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="46">
         <f>Modell!$B$4/Modell!AF18</f>
-        <v>60.031895466290692</v>
-      </c>
-      <c r="E9" s="48">
+        <v>70.368513228698362</v>
+      </c>
+      <c r="E9" s="46">
         <f>Modell!$B$4/Modell!AG18</f>
-        <v>35.493526421216714</v>
-      </c>
-      <c r="F9" s="48">
+        <v>41.604994546724228</v>
+      </c>
+      <c r="F9" s="46">
         <f>Modell!$B$4/Modell!AH18</f>
-        <v>23.499163556251485</v>
+        <v>27.545377148718629</v>
       </c>
     </row>
   </sheetData>
@@ -14275,7 +14782,7 @@
   <sheetData>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>3</v>
@@ -14326,25 +14833,25 @@
         <v>93</v>
       </c>
       <c r="S3" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="T3" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="T3" s="21" t="s">
+      <c r="U3" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="U3" s="21" t="s">
+      <c r="V3" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="V3" s="21" t="s">
-        <v>183</v>
-      </c>
       <c r="Y3" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z3" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="AA3" s="21" t="s">
         <v>278</v>
-      </c>
-      <c r="AA3" s="21" t="s">
-        <v>279</v>
       </c>
       <c r="AB3" s="21" t="s">
         <v>115</v>
@@ -14373,7 +14880,7 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:35" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -14559,7 +15066,7 @@
     <row r="7" spans="1:35" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" s="18">
         <v>128.76900000000001</v>
@@ -14648,7 +15155,7 @@
     </row>
     <row r="8" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" s="10">
         <v>0.65</v>
@@ -14739,107 +15246,107 @@
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77">
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75">
         <f>(G5-C5)/C5</f>
         <v>-0.21945147699907469</v>
       </c>
-      <c r="H10" s="77">
+      <c r="H10" s="75">
         <f t="shared" ref="H10:S10" si="0">(H5-D5)/D5</f>
         <v>-0.15981687523979082</v>
       </c>
-      <c r="I10" s="77">
+      <c r="I10" s="75">
         <f t="shared" si="0"/>
         <v>-8.0023430067948917E-2</v>
       </c>
-      <c r="J10" s="77">
+      <c r="J10" s="75">
         <f t="shared" si="0"/>
         <v>-1.1380199618087681E-2</v>
       </c>
-      <c r="K10" s="77">
+      <c r="K10" s="75">
         <f t="shared" si="0"/>
         <v>5.3555469913652037E-2</v>
       </c>
-      <c r="L10" s="77">
+      <c r="L10" s="75">
         <f t="shared" si="0"/>
         <v>0.11669380881868537</v>
       </c>
-      <c r="M10" s="77">
+      <c r="M10" s="75">
         <f t="shared" si="0"/>
         <v>5.5810362835475191E-2</v>
       </c>
-      <c r="N10" s="77">
+      <c r="N10" s="75">
         <f t="shared" si="0"/>
         <v>6.7560990957193146E-2</v>
       </c>
-      <c r="O10" s="77">
+      <c r="O10" s="75">
         <f t="shared" si="0"/>
         <v>-1.1191443884102793E-3</v>
       </c>
-      <c r="P10" s="77">
+      <c r="P10" s="75">
         <f t="shared" si="0"/>
         <v>5.4663729752429772E-2</v>
       </c>
-      <c r="Q10" s="77">
+      <c r="Q10" s="75">
         <f t="shared" si="0"/>
         <v>6.2774193548387133E-2</v>
       </c>
-      <c r="R10" s="77">
+      <c r="R10" s="75">
         <f t="shared" si="0"/>
         <v>6.057253110138517E-2</v>
       </c>
-      <c r="S10" s="77">
+      <c r="S10" s="75">
         <f t="shared" si="0"/>
         <v>7.4397612720281378E-2</v>
       </c>
-      <c r="T10" s="77">
+      <c r="T10" s="75">
         <f>(T5-P5)/P5</f>
         <v>6.9295802136963958E-2</v>
       </c>
-      <c r="Y10" s="77"/>
-      <c r="Z10" s="77">
+      <c r="Y10" s="75"/>
+      <c r="Z10" s="75">
         <f t="shared" ref="Z10:AG10" si="1">(Z5-Y5)/Y5</f>
         <v>0.1555018463357111</v>
       </c>
-      <c r="AA10" s="77">
+      <c r="AA10" s="75">
         <f t="shared" si="1"/>
         <v>8.6276127709192227E-2</v>
       </c>
-      <c r="AB10" s="77">
+      <c r="AB10" s="75">
         <f t="shared" si="1"/>
         <v>6.7255144850558862E-2</v>
       </c>
-      <c r="AC10" s="77">
+      <c r="AC10" s="75">
         <f t="shared" si="1"/>
         <v>0.76496706320309726</v>
       </c>
-      <c r="AD10" s="77">
+      <c r="AD10" s="75">
         <f t="shared" si="1"/>
         <v>4.3566230963739586E-2</v>
       </c>
-      <c r="AE10" s="77">
+      <c r="AE10" s="75">
         <f t="shared" si="1"/>
         <v>-0.17191491271552914</v>
       </c>
-      <c r="AF10" s="77">
+      <c r="AF10" s="75">
         <f t="shared" si="1"/>
         <v>-5.2954535740362484E-2</v>
       </c>
-      <c r="AG10" s="77">
+      <c r="AG10" s="75">
         <f t="shared" si="1"/>
         <v>5.9656849755971145E-2</v>
       </c>
-      <c r="AH10" s="77">
+      <c r="AH10" s="75">
         <f t="shared" ref="AH10" si="2">(AH5-AG5)/AG5</f>
         <v>6.2759006783903226E-2</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C11" s="11">
         <f t="shared" ref="C11:R11" si="3">C6/C5</f>
@@ -14956,7 +15463,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C12" s="11">
         <f t="shared" ref="C12:R12" si="7">C7/C5</f>
@@ -15162,7 +15669,7 @@
     </row>
     <row r="15" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G15" s="11">
         <f t="shared" ref="G15:S15" si="11">(G14-C14)/C14</f>
@@ -15260,7 +15767,7 @@
     <row r="17" spans="1:34" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C17" s="18">
         <v>164.84800000000001</v>
@@ -15350,7 +15857,7 @@
     <row r="18" spans="1:34" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C18" s="18">
         <v>-98.811999999999998</v>
@@ -15439,8 +15946,8 @@
     </row>
     <row r="19" spans="1:34" s="18" customFormat="1" ht="20" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="78" t="s">
-        <v>280</v>
+      <c r="B19" s="76" t="s">
+        <v>279</v>
       </c>
       <c r="C19" s="18">
         <v>2.4</v>
@@ -15530,7 +16037,7 @@
     <row r="20" spans="1:34" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C20" s="18">
         <v>-100.666</v>
@@ -15619,8 +16126,8 @@
     </row>
     <row r="21" spans="1:34" s="18" customFormat="1" ht="40" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="78" t="s">
-        <v>281</v>
+      <c r="B21" s="76" t="s">
+        <v>280</v>
       </c>
       <c r="C21" s="18">
         <v>-26.628</v>
@@ -15707,120 +16214,120 @@
         <v>49.651000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:34" s="81" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="80"/>
-      <c r="B22" s="81" t="s">
+    <row r="22" spans="1:34" s="79" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="78"/>
+      <c r="B22" s="79" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="81">
+      <c r="C22" s="79">
         <f t="shared" ref="C22:S22" si="13">SUM(C17:C21)</f>
         <v>-58.857999999999976</v>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="79">
         <f t="shared" si="13"/>
         <v>-173.79900000000001</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="79">
         <f t="shared" si="13"/>
         <v>-72.039999999999992</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="79">
         <f t="shared" si="13"/>
         <v>74.644999999999996</v>
       </c>
-      <c r="G22" s="81">
+      <c r="G22" s="79">
         <f t="shared" si="13"/>
         <v>127.59799999999997</v>
       </c>
-      <c r="H22" s="81">
+      <c r="H22" s="79">
         <f t="shared" si="13"/>
         <v>117.42299999999996</v>
       </c>
-      <c r="I22" s="81">
+      <c r="I22" s="79">
         <f t="shared" si="13"/>
         <v>33.751999999999995</v>
       </c>
-      <c r="J22" s="81">
+      <c r="J22" s="79">
         <f t="shared" si="13"/>
         <v>177.62599999999998</v>
       </c>
-      <c r="K22" s="81">
+      <c r="K22" s="79">
         <f t="shared" si="13"/>
         <v>60.571000000000012</v>
       </c>
-      <c r="L22" s="81">
+      <c r="L22" s="79">
         <f t="shared" si="13"/>
         <v>-21.522999999999996</v>
       </c>
-      <c r="M22" s="81">
+      <c r="M22" s="79">
         <f t="shared" si="13"/>
         <v>-30.956000000000003</v>
       </c>
-      <c r="N22" s="81">
+      <c r="N22" s="79">
         <f t="shared" si="13"/>
         <v>122.01300000000001</v>
       </c>
-      <c r="O22" s="81">
+      <c r="O22" s="79">
         <f t="shared" si="13"/>
         <v>-86.773999999999987</v>
       </c>
-      <c r="P22" s="81">
+      <c r="P22" s="79">
         <f t="shared" si="13"/>
         <v>-86.138000000000005</v>
       </c>
-      <c r="Q22" s="81">
+      <c r="Q22" s="79">
         <f t="shared" si="13"/>
         <v>-2.1650000000000063</v>
       </c>
-      <c r="R22" s="81">
+      <c r="R22" s="79">
         <f t="shared" si="13"/>
         <v>202.91199999999998</v>
       </c>
-      <c r="S22" s="81">
+      <c r="S22" s="79">
         <f t="shared" si="13"/>
         <v>-8.846000000000025</v>
       </c>
-      <c r="T22" s="81">
+      <c r="T22" s="79">
         <f>SUM(T17:T21)</f>
         <v>-130.953</v>
       </c>
-      <c r="Y22" s="81">
+      <c r="Y22" s="79">
         <f t="shared" ref="Y22:AG22" si="14">SUM(Y17:Y21)</f>
         <v>7.0950000000000131</v>
       </c>
-      <c r="Z22" s="81">
+      <c r="Z22" s="79">
         <f t="shared" si="14"/>
         <v>35.087000000000003</v>
       </c>
-      <c r="AA22" s="81">
+      <c r="AA22" s="79">
         <f t="shared" si="14"/>
         <v>-57.005000000000003</v>
       </c>
-      <c r="AB22" s="81">
+      <c r="AB22" s="79">
         <f t="shared" si="14"/>
         <v>23.208999999999993</v>
       </c>
-      <c r="AC22" s="81">
+      <c r="AC22" s="79">
         <f t="shared" si="14"/>
         <v>298.46600000000007</v>
       </c>
-      <c r="AD22" s="81">
+      <c r="AD22" s="79">
         <f t="shared" si="14"/>
         <v>-591.86199999999997</v>
       </c>
-      <c r="AE22" s="81">
+      <c r="AE22" s="79">
         <f t="shared" si="14"/>
         <v>-43.629999999999939</v>
       </c>
-      <c r="AF22" s="81">
+      <c r="AF22" s="79">
         <f t="shared" si="14"/>
         <v>389.43299999999999</v>
       </c>
-      <c r="AG22" s="81">
+      <c r="AG22" s="79">
         <f t="shared" si="14"/>
         <v>-17.342000000000006</v>
       </c>
-      <c r="AH22" s="81">
+      <c r="AH22" s="79">
         <f>SUM(AH17:AH21)</f>
         <v>105.71200000000002</v>
       </c>
@@ -15830,7 +16337,7 @@
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:34" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16013,7 +16520,7 @@
     </row>
     <row r="28" spans="1:34" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C28" s="18">
         <v>196.982</v>
@@ -16100,92 +16607,92 @@
         <v>1876.076</v>
       </c>
     </row>
-    <row r="29" spans="1:34" s="79" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="79" t="s">
-        <v>269</v>
-      </c>
-      <c r="C29" s="79">
+    <row r="29" spans="1:34" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="77" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="77">
         <v>1.06</v>
       </c>
-      <c r="D29" s="79">
+      <c r="D29" s="77">
         <v>1.34</v>
       </c>
-      <c r="E29" s="79">
+      <c r="E29" s="77">
         <v>1.0900000000000001</v>
       </c>
-      <c r="F29" s="79">
+      <c r="F29" s="77">
         <v>1.53</v>
       </c>
-      <c r="G29" s="79">
+      <c r="G29" s="77">
         <v>1.05</v>
       </c>
-      <c r="H29" s="79">
+      <c r="H29" s="77">
         <v>1.51</v>
       </c>
-      <c r="I29" s="79">
+      <c r="I29" s="77">
         <v>1.34</v>
       </c>
-      <c r="J29" s="79">
+      <c r="J29" s="77">
         <v>2.83</v>
       </c>
-      <c r="K29" s="79">
+      <c r="K29" s="77">
         <v>1.44</v>
       </c>
-      <c r="L29" s="79">
+      <c r="L29" s="77">
         <v>1.57</v>
       </c>
-      <c r="M29" s="79">
+      <c r="M29" s="77">
         <v>2.08</v>
       </c>
-      <c r="N29" s="79">
+      <c r="N29" s="77">
         <v>2.27</v>
       </c>
-      <c r="O29" s="79">
+      <c r="O29" s="77">
         <v>1.73</v>
       </c>
-      <c r="P29" s="79">
+      <c r="P29" s="77">
         <v>2.08</v>
       </c>
-      <c r="Q29" s="79">
+      <c r="Q29" s="77">
         <v>2.09</v>
       </c>
-      <c r="R29" s="79">
+      <c r="R29" s="77">
         <v>2.75</v>
       </c>
-      <c r="S29" s="79">
+      <c r="S29" s="77">
         <v>2.1</v>
       </c>
-      <c r="T29" s="79">
+      <c r="T29" s="77">
         <v>2.8</v>
       </c>
-      <c r="Y29" s="79">
+      <c r="Y29" s="77">
         <v>2.73</v>
       </c>
-      <c r="Z29" s="79">
+      <c r="Z29" s="77">
         <v>3.76</v>
       </c>
-      <c r="AA29" s="79">
+      <c r="AA29" s="77">
         <v>3.66</v>
       </c>
-      <c r="AB29" s="79">
+      <c r="AB29" s="77">
         <v>4.99</v>
       </c>
-      <c r="AC29" s="79">
+      <c r="AC29" s="77">
         <v>5.17</v>
       </c>
-      <c r="AD29" s="79">
+      <c r="AD29" s="77">
         <v>5.63</v>
       </c>
-      <c r="AE29" s="79">
+      <c r="AE29" s="77">
         <v>5.0599999999999996</v>
       </c>
-      <c r="AF29" s="79">
+      <c r="AF29" s="77">
         <v>6.74</v>
       </c>
-      <c r="AG29" s="79">
+      <c r="AG29" s="77">
         <v>7.35</v>
       </c>
-      <c r="AH29" s="79">
+      <c r="AH29" s="77">
         <v>8.65</v>
       </c>
     </row>
@@ -16195,100 +16702,100 @@
       <c r="Z30" s="16"/>
       <c r="AA30" s="16"/>
     </row>
-    <row r="31" spans="1:34" s="77" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:34" s="75" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="G31" s="77">
+      <c r="G31" s="75">
         <f t="shared" ref="G31:T31" si="15">(G26-C26)/C26</f>
         <v>0</v>
       </c>
-      <c r="H31" s="77">
+      <c r="H31" s="75">
         <f t="shared" si="15"/>
         <v>6.4442193268554257E-2</v>
       </c>
-      <c r="I31" s="77">
+      <c r="I31" s="75">
         <f t="shared" si="15"/>
         <v>0.1202147603456228</v>
       </c>
-      <c r="J31" s="77">
+      <c r="J31" s="75">
         <f t="shared" si="15"/>
         <v>0.13483690510090662</v>
       </c>
-      <c r="K31" s="77">
+      <c r="K31" s="75">
         <f t="shared" si="15"/>
         <v>0.20413116685723839</v>
       </c>
-      <c r="L31" s="77">
+      <c r="L31" s="75">
         <f t="shared" si="15"/>
         <v>0.14073039343728586</v>
       </c>
-      <c r="M31" s="77">
+      <c r="M31" s="75">
         <f t="shared" si="15"/>
         <v>0.24147437518150244</v>
       </c>
-      <c r="N31" s="77">
+      <c r="N31" s="75">
         <f t="shared" si="15"/>
         <v>0.22938197006275204</v>
       </c>
-      <c r="O31" s="77">
+      <c r="O31" s="75">
         <f t="shared" si="15"/>
         <v>0.11106294000864189</v>
       </c>
-      <c r="P31" s="77">
+      <c r="P31" s="75">
         <f t="shared" si="15"/>
         <v>0.20435317332051922</v>
       </c>
-      <c r="Q31" s="77">
+      <c r="Q31" s="75">
         <f t="shared" si="15"/>
         <v>0.11656773991785747</v>
       </c>
-      <c r="R31" s="77">
+      <c r="R31" s="75">
         <f t="shared" si="15"/>
         <v>0.16591772012992714</v>
       </c>
-      <c r="S31" s="77">
+      <c r="S31" s="75">
         <f t="shared" si="15"/>
         <v>0.14226444027388468</v>
       </c>
-      <c r="T31" s="77">
+      <c r="T31" s="75">
         <f t="shared" si="15"/>
         <v>0.11436796938548324</v>
       </c>
-      <c r="Z31" s="77">
+      <c r="Z31" s="75">
         <f>(Z26-Y26)/Y26</f>
         <v>2.4874605891331537E-2</v>
       </c>
-      <c r="AA31" s="77">
+      <c r="AA31" s="75">
         <f t="shared" ref="AA31:AH31" si="16">(AA26-Z26)/Z26</f>
         <v>7.2362536680377759E-2</v>
       </c>
-      <c r="AB31" s="77">
+      <c r="AB31" s="75">
         <f t="shared" si="16"/>
         <v>0.12249973412549998</v>
       </c>
-      <c r="AC31" s="77">
+      <c r="AC31" s="75">
         <f t="shared" si="16"/>
         <v>0.11418960187677733</v>
       </c>
-      <c r="AD31" s="77">
+      <c r="AD31" s="75">
         <f t="shared" si="16"/>
         <v>0.19018466894044359</v>
       </c>
-      <c r="AE31" s="77">
+      <c r="AE31" s="75">
         <f t="shared" si="16"/>
         <v>-2.4586401808623475E-2</v>
       </c>
-      <c r="AF31" s="77">
+      <c r="AF31" s="75">
         <f t="shared" si="16"/>
         <v>7.5708713437851266E-2</v>
       </c>
-      <c r="AG31" s="77">
+      <c r="AG31" s="75">
         <f t="shared" si="16"/>
         <v>0.20439929062332873</v>
       </c>
-      <c r="AH31" s="77">
+      <c r="AH31" s="75">
         <f t="shared" si="16"/>
         <v>0.15064802491002321</v>
       </c>
@@ -16296,7 +16803,7 @@
     <row r="32" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C32" s="11">
         <f t="shared" ref="C32:R32" si="17">C27/C26</f>
@@ -16414,7 +16921,7 @@
     <row r="33" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18"/>
       <c r="B33" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C33" s="11">
         <f t="shared" ref="C33:R33" si="20">C28/C26</f>
@@ -16621,7 +17128,7 @@
     </row>
     <row r="36" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G36" s="11">
         <f t="shared" ref="G36:R36" si="23">(G35-C35)/C35</f>
@@ -16719,7 +17226,7 @@
     <row r="38" spans="1:35" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C38" s="18">
         <v>46.872999999999998</v>
@@ -16809,7 +17316,7 @@
     <row r="39" spans="1:35" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="18">
         <v>43.712000000000003</v>
@@ -16898,8 +17405,8 @@
     </row>
     <row r="40" spans="1:35" s="18" customFormat="1" ht="40" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="78" t="s">
-        <v>274</v>
+      <c r="B40" s="76" t="s">
+        <v>273</v>
       </c>
       <c r="C40" s="18">
         <v>4.78</v>
@@ -16989,7 +17496,7 @@
     <row r="41" spans="1:35" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C41" s="18">
         <v>-4.2</v>
@@ -17078,8 +17585,8 @@
     </row>
     <row r="42" spans="1:35" s="18" customFormat="1" ht="40" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="78" t="s">
-        <v>276</v>
+      <c r="B42" s="76" t="s">
+        <v>275</v>
       </c>
       <c r="C42" s="18">
         <v>-67.405000000000001</v>
@@ -17364,7 +17871,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
@@ -17433,7 +17940,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="49">
+      <c r="A5" s="47">
         <f>W27</f>
         <v>121.96478052641898</v>
       </c>
@@ -17506,7 +18013,7 @@
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <f>W28</f>
-        <v>-0.19228622167934453</v>
+        <v>-0.3109334433535651</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>21</v>
@@ -19614,7 +20121,7 @@
     </row>
     <row r="25" spans="3:254" x14ac:dyDescent="0.25">
       <c r="V25" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W25" s="29">
         <f>W24*Modell!B11</f>
@@ -19644,7 +20151,7 @@
       </c>
       <c r="W28" s="12">
         <f>(W27-Modell!B4)/Modell!B4</f>
-        <v>-0.19228622167934453</v>
+        <v>-0.3109334433535651</v>
       </c>
     </row>
   </sheetData>
